--- a/Excel/LifeShieldConfig.xlsx
+++ b/Excel/LifeShieldConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C737FD-CFF0-4072-BC27-3E6128FC899F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7E7324-E134-4CC7-B636-740C94CB6EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LifeShieldProto" sheetId="1" r:id="rId1"/>
@@ -1917,36 +1917,6 @@
     <t>Anger Soul Level 32</t>
   </si>
   <si>
-    <t>Life Spirit Level 1</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 2</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 8</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 10</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 16</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 22</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 24</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 25</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 28</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 35</t>
-  </si>
-  <si>
     <t>Lava Soul Level 1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2467,81 +2437,6 @@
     <t>Expulsion Soul level 35</t>
   </si>
   <si>
-    <t>Life Spirit Level 3</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 4</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 5</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 6</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 7</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 9</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 11</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 12</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 13</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 14</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 15</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 17</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 18</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 19</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 20</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 21</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 23</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 26</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 27</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 29</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 30</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 31</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 32</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 33</t>
-  </si>
-  <si>
-    <t>Life Spirit Level 34</t>
-  </si>
-  <si>
     <t>额外描述2</t>
   </si>
   <si>
@@ -3212,6 +3107,111 @@
   <si>
     <t>Maximum HP increased by 35%, and 35% chance to resist</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Life Soul Level 1</t>
+  </si>
+  <si>
+    <t>Life Soul Level 2</t>
+  </si>
+  <si>
+    <t>Life Soul Level 3</t>
+  </si>
+  <si>
+    <t>Life Soul Level 4</t>
+  </si>
+  <si>
+    <t>Life Soul Level 5</t>
+  </si>
+  <si>
+    <t>Life Soul Level 6</t>
+  </si>
+  <si>
+    <t>Life Soul Level 7</t>
+  </si>
+  <si>
+    <t>Life Soul Level 8</t>
+  </si>
+  <si>
+    <t>Life Soul Level 9</t>
+  </si>
+  <si>
+    <t>Life Soul Level 10</t>
+  </si>
+  <si>
+    <t>Life Soul Level 11</t>
+  </si>
+  <si>
+    <t>Life Soul Level 12</t>
+  </si>
+  <si>
+    <t>Life Soul Level 13</t>
+  </si>
+  <si>
+    <t>Life Soul Level 14</t>
+  </si>
+  <si>
+    <t>Life Soul Level 15</t>
+  </si>
+  <si>
+    <t>Life Soul Level 16</t>
+  </si>
+  <si>
+    <t>Life Soul Level 17</t>
+  </si>
+  <si>
+    <t>Life Soul Level 18</t>
+  </si>
+  <si>
+    <t>Life Soul Level 19</t>
+  </si>
+  <si>
+    <t>Life Soul Level 20</t>
+  </si>
+  <si>
+    <t>Life Soul Level 21</t>
+  </si>
+  <si>
+    <t>Life Soul Level 22</t>
+  </si>
+  <si>
+    <t>Life Soul Level 23</t>
+  </si>
+  <si>
+    <t>Life Soul Level 24</t>
+  </si>
+  <si>
+    <t>Life Soul Level 25</t>
+  </si>
+  <si>
+    <t>Life Soul Level 26</t>
+  </si>
+  <si>
+    <t>Life Soul Level 27</t>
+  </si>
+  <si>
+    <t>Life Soul Level 28</t>
+  </si>
+  <si>
+    <t>Life Soul Level 29</t>
+  </si>
+  <si>
+    <t>Life Soul Level 30</t>
+  </si>
+  <si>
+    <t>Life Soul Level 31</t>
+  </si>
+  <si>
+    <t>Life Soul Level 32</t>
+  </si>
+  <si>
+    <t>Life Soul Level 33</t>
+  </si>
+  <si>
+    <t>Life Soul Level 34</t>
+  </si>
+  <si>
+    <t>Life Soul Level 35</t>
   </si>
 </sst>
 </file>
@@ -5219,7 +5219,7 @@
         <v>7</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>824</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5248,7 +5248,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>825</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5291,7 +5291,7 @@
         <v>16</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -5306,7 +5306,7 @@
         <v>18</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>826</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5320,7 +5320,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="G7" s="5">
         <v>2</v>
@@ -5335,7 +5335,7 @@
         <v>21</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>827</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5364,7 +5364,7 @@
         <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>828</v>
+        <v>793</v>
       </c>
     </row>
     <row r="9" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5378,7 +5378,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="G9" s="5">
         <v>4</v>
@@ -5393,7 +5393,7 @@
         <v>27</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>829</v>
+        <v>794</v>
       </c>
     </row>
     <row r="10" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5422,7 +5422,7 @@
         <v>30</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>830</v>
+        <v>795</v>
       </c>
     </row>
     <row r="11" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5436,7 +5436,7 @@
         <v>31</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="G11" s="5">
         <v>6</v>
@@ -5451,7 +5451,7 @@
         <v>33</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>831</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5480,7 +5480,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>832</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5494,7 +5494,7 @@
         <v>37</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="G13" s="5">
         <v>8</v>
@@ -5509,7 +5509,7 @@
         <v>39</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>833</v>
+        <v>798</v>
       </c>
     </row>
     <row r="14" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5523,7 +5523,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="G14" s="5">
         <v>9</v>
@@ -5538,7 +5538,7 @@
         <v>42</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>834</v>
+        <v>799</v>
       </c>
     </row>
     <row r="15" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5552,7 +5552,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="G15" s="5">
         <v>10</v>
@@ -5567,7 +5567,7 @@
         <v>45</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>835</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5581,7 +5581,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="G16" s="5">
         <v>11</v>
@@ -5596,7 +5596,7 @@
         <v>48</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>836</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5610,7 +5610,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="G17" s="5">
         <v>12</v>
@@ -5625,7 +5625,7 @@
         <v>51</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>837</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5639,7 +5639,7 @@
         <v>52</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="G18" s="5">
         <v>13</v>
@@ -5654,7 +5654,7 @@
         <v>54</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>838</v>
+        <v>803</v>
       </c>
     </row>
     <row r="19" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5668,7 +5668,7 @@
         <v>55</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="G19" s="5">
         <v>14</v>
@@ -5683,7 +5683,7 @@
         <v>57</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5697,7 +5697,7 @@
         <v>58</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="G20" s="5">
         <v>15</v>
@@ -5712,7 +5712,7 @@
         <v>60</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>840</v>
+        <v>805</v>
       </c>
     </row>
     <row r="21" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5727,7 +5727,7 @@
         <v>61</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="G21" s="5">
         <f>G20+1</f>
@@ -5743,7 +5743,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
     </row>
     <row r="22" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5758,7 +5758,7 @@
         <v>64</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" ref="G22:G40" si="1">G21+1</f>
@@ -5774,7 +5774,7 @@
         <v>66</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>842</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5805,7 +5805,7 @@
         <v>69</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>843</v>
+        <v>808</v>
       </c>
     </row>
     <row r="24" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5820,7 +5820,7 @@
         <v>70</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
@@ -5836,7 +5836,7 @@
         <v>72</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>844</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5851,7 +5851,7 @@
         <v>73</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
@@ -5867,7 +5867,7 @@
         <v>75</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>845</v>
+        <v>810</v>
       </c>
     </row>
     <row r="26" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5882,7 +5882,7 @@
         <v>76</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
@@ -5898,7 +5898,7 @@
         <v>78</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>846</v>
+        <v>811</v>
       </c>
     </row>
     <row r="27" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5913,7 +5913,7 @@
         <v>79</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
@@ -5929,7 +5929,7 @@
         <v>81</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>847</v>
+        <v>812</v>
       </c>
     </row>
     <row r="28" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5960,7 +5960,7 @@
         <v>84</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>848</v>
+        <v>813</v>
       </c>
     </row>
     <row r="29" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -5975,7 +5975,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
@@ -5991,7 +5991,7 @@
         <v>87</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>849</v>
+        <v>814</v>
       </c>
     </row>
     <row r="30" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6006,7 +6006,7 @@
         <v>88</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
@@ -6022,7 +6022,7 @@
         <v>90</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>850</v>
+        <v>815</v>
       </c>
     </row>
     <row r="31" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6037,7 +6037,7 @@
         <v>91</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
@@ -6053,7 +6053,7 @@
         <v>93</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>851</v>
+        <v>816</v>
       </c>
     </row>
     <row r="32" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6068,7 +6068,7 @@
         <v>94</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
@@ -6084,7 +6084,7 @@
         <v>96</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>852</v>
+        <v>817</v>
       </c>
     </row>
     <row r="33" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6099,7 +6099,7 @@
         <v>97</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
@@ -6115,7 +6115,7 @@
         <v>99</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>853</v>
+        <v>818</v>
       </c>
     </row>
     <row r="34" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6130,7 +6130,7 @@
         <v>100</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="1"/>
@@ -6146,7 +6146,7 @@
         <v>102</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>854</v>
+        <v>819</v>
       </c>
     </row>
     <row r="35" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6161,7 +6161,7 @@
         <v>103</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="1"/>
@@ -6177,7 +6177,7 @@
         <v>105</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>855</v>
+        <v>820</v>
       </c>
     </row>
     <row r="36" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6192,7 +6192,7 @@
         <v>106</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="1"/>
@@ -6208,7 +6208,7 @@
         <v>108</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>856</v>
+        <v>821</v>
       </c>
     </row>
     <row r="37" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6223,7 +6223,7 @@
         <v>109</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="1"/>
@@ -6239,7 +6239,7 @@
         <v>111</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>857</v>
+        <v>822</v>
       </c>
     </row>
     <row r="38" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6254,7 +6254,7 @@
         <v>112</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="1"/>
@@ -6270,7 +6270,7 @@
         <v>114</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>858</v>
+        <v>823</v>
       </c>
     </row>
     <row r="39" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6285,7 +6285,7 @@
         <v>115</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="1"/>
@@ -6301,7 +6301,7 @@
         <v>117</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>859</v>
+        <v>824</v>
       </c>
     </row>
     <row r="40" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6316,7 +6316,7 @@
         <v>118</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="1"/>
@@ -6332,7 +6332,7 @@
         <v>120</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>860</v>
+        <v>825</v>
       </c>
     </row>
     <row r="41" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6361,7 +6361,7 @@
         <v>123</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>861</v>
+        <v>826</v>
       </c>
     </row>
     <row r="42" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6390,7 +6390,7 @@
         <v>126</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>862</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6404,7 +6404,7 @@
         <v>127</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="G43" s="5">
         <v>3</v>
@@ -6419,7 +6419,7 @@
         <v>129</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>863</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6433,7 +6433,7 @@
         <v>130</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="G44" s="5">
         <v>4</v>
@@ -6448,7 +6448,7 @@
         <v>132</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>864</v>
+        <v>829</v>
       </c>
     </row>
     <row r="45" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6477,7 +6477,7 @@
         <v>135</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>865</v>
+        <v>830</v>
       </c>
     </row>
     <row r="46" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6491,7 +6491,7 @@
         <v>136</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G46" s="5">
         <v>6</v>
@@ -6506,7 +6506,7 @@
         <v>138</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>866</v>
+        <v>831</v>
       </c>
     </row>
     <row r="47" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6520,7 +6520,7 @@
         <v>139</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="G47" s="5">
         <v>7</v>
@@ -6535,7 +6535,7 @@
         <v>141</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>867</v>
+        <v>832</v>
       </c>
     </row>
     <row r="48" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6549,7 +6549,7 @@
         <v>142</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="G48" s="5">
         <v>8</v>
@@ -6564,7 +6564,7 @@
         <v>144</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>868</v>
+        <v>833</v>
       </c>
     </row>
     <row r="49" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6578,7 +6578,7 @@
         <v>145</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="G49" s="5">
         <v>9</v>
@@ -6593,7 +6593,7 @@
         <v>147</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>869</v>
+        <v>834</v>
       </c>
     </row>
     <row r="50" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6607,7 +6607,7 @@
         <v>148</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="G50" s="5">
         <v>10</v>
@@ -6622,7 +6622,7 @@
         <v>150</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>870</v>
+        <v>835</v>
       </c>
     </row>
     <row r="51" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6636,7 +6636,7 @@
         <v>151</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="G51" s="5">
         <v>11</v>
@@ -6651,7 +6651,7 @@
         <v>153</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>871</v>
+        <v>836</v>
       </c>
     </row>
     <row r="52" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6680,7 +6680,7 @@
         <v>156</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>872</v>
+        <v>837</v>
       </c>
     </row>
     <row r="53" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6709,7 +6709,7 @@
         <v>159</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>873</v>
+        <v>838</v>
       </c>
     </row>
     <row r="54" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6723,7 +6723,7 @@
         <v>160</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="G54" s="5">
         <v>14</v>
@@ -6738,7 +6738,7 @@
         <v>162</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>874</v>
+        <v>839</v>
       </c>
     </row>
     <row r="55" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6767,7 +6767,7 @@
         <v>165</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>875</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6779,10 +6779,10 @@
         <v>2</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="G56" s="5">
         <f>G55+1</f>
@@ -6798,7 +6798,7 @@
         <v>167</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>876</v>
+        <v>841</v>
       </c>
     </row>
     <row r="57" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6810,10 +6810,10 @@
         <v>2</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="G57" s="5">
         <f t="shared" ref="G57:G75" si="3">G56+1</f>
@@ -6829,7 +6829,7 @@
         <v>169</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>877</v>
+        <v>842</v>
       </c>
     </row>
     <row r="58" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6841,10 +6841,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="G58" s="5">
         <f t="shared" si="3"/>
@@ -6860,7 +6860,7 @@
         <v>171</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>878</v>
+        <v>843</v>
       </c>
     </row>
     <row r="59" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6872,10 +6872,10 @@
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="G59" s="5">
         <f t="shared" si="3"/>
@@ -6891,7 +6891,7 @@
         <v>173</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>879</v>
+        <v>844</v>
       </c>
     </row>
     <row r="60" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6903,10 +6903,10 @@
         <v>2</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="G60" s="5">
         <f t="shared" si="3"/>
@@ -6922,7 +6922,7 @@
         <v>175</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>880</v>
+        <v>845</v>
       </c>
     </row>
     <row r="61" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6934,10 +6934,10 @@
         <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="G61" s="5">
         <f t="shared" si="3"/>
@@ -6953,7 +6953,7 @@
         <v>177</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>881</v>
+        <v>846</v>
       </c>
     </row>
     <row r="62" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6965,10 +6965,10 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G62" s="5">
         <f t="shared" si="3"/>
@@ -6984,7 +6984,7 @@
         <v>179</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>882</v>
+        <v>847</v>
       </c>
     </row>
     <row r="63" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -6996,10 +6996,10 @@
         <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="G63" s="5">
         <f t="shared" si="3"/>
@@ -7015,7 +7015,7 @@
         <v>181</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>883</v>
+        <v>848</v>
       </c>
     </row>
     <row r="64" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7027,10 +7027,10 @@
         <v>2</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="G64" s="5">
         <f t="shared" si="3"/>
@@ -7046,7 +7046,7 @@
         <v>183</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>884</v>
+        <v>849</v>
       </c>
     </row>
     <row r="65" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7058,10 +7058,10 @@
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" si="3"/>
@@ -7077,7 +7077,7 @@
         <v>185</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>885</v>
+        <v>850</v>
       </c>
     </row>
     <row r="66" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7089,10 +7089,10 @@
         <v>2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="G66" s="5">
         <f t="shared" si="3"/>
@@ -7108,7 +7108,7 @@
         <v>187</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>886</v>
+        <v>851</v>
       </c>
     </row>
     <row r="67" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7120,10 +7120,10 @@
         <v>2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="G67" s="5">
         <f t="shared" si="3"/>
@@ -7139,7 +7139,7 @@
         <v>189</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>887</v>
+        <v>852</v>
       </c>
     </row>
     <row r="68" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7151,10 +7151,10 @@
         <v>2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" si="3"/>
@@ -7170,7 +7170,7 @@
         <v>191</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>888</v>
+        <v>853</v>
       </c>
     </row>
     <row r="69" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7182,10 +7182,10 @@
         <v>2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="3"/>
@@ -7201,7 +7201,7 @@
         <v>193</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>889</v>
+        <v>854</v>
       </c>
     </row>
     <row r="70" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7213,10 +7213,10 @@
         <v>2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="3"/>
@@ -7232,7 +7232,7 @@
         <v>195</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>890</v>
+        <v>855</v>
       </c>
     </row>
     <row r="71" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7244,10 +7244,10 @@
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="3"/>
@@ -7263,7 +7263,7 @@
         <v>197</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>891</v>
+        <v>856</v>
       </c>
     </row>
     <row r="72" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7275,10 +7275,10 @@
         <v>2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="3"/>
@@ -7294,7 +7294,7 @@
         <v>199</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>892</v>
+        <v>857</v>
       </c>
     </row>
     <row r="73" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7306,10 +7306,10 @@
         <v>2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="3"/>
@@ -7325,7 +7325,7 @@
         <v>201</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>893</v>
+        <v>858</v>
       </c>
     </row>
     <row r="74" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7337,10 +7337,10 @@
         <v>2</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="G74" s="5">
         <f t="shared" si="3"/>
@@ -7356,7 +7356,7 @@
         <v>203</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>894</v>
+        <v>859</v>
       </c>
     </row>
     <row r="75" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7368,10 +7368,10 @@
         <v>2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="G75" s="5">
         <f t="shared" si="3"/>
@@ -7387,7 +7387,7 @@
         <v>205</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>895</v>
+        <v>860</v>
       </c>
     </row>
     <row r="76" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7401,7 +7401,7 @@
         <v>206</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="G76" s="5">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>208</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>896</v>
+        <v>861</v>
       </c>
     </row>
     <row r="77" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7430,7 +7430,7 @@
         <v>209</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="G77" s="5">
         <v>2</v>
@@ -7445,7 +7445,7 @@
         <v>211</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>897</v>
+        <v>862</v>
       </c>
     </row>
     <row r="78" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7459,7 +7459,7 @@
         <v>212</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="G78" s="5">
         <v>3</v>
@@ -7474,7 +7474,7 @@
         <v>214</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>898</v>
+        <v>863</v>
       </c>
     </row>
     <row r="79" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7488,7 +7488,7 @@
         <v>215</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="G79" s="5">
         <v>4</v>
@@ -7503,7 +7503,7 @@
         <v>217</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>899</v>
+        <v>864</v>
       </c>
     </row>
     <row r="80" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7517,7 +7517,7 @@
         <v>218</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G80" s="5">
         <v>5</v>
@@ -7532,7 +7532,7 @@
         <v>220</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>900</v>
+        <v>865</v>
       </c>
     </row>
     <row r="81" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7546,7 +7546,7 @@
         <v>221</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="G81" s="5">
         <v>6</v>
@@ -7561,7 +7561,7 @@
         <v>223</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>901</v>
+        <v>866</v>
       </c>
     </row>
     <row r="82" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7575,7 +7575,7 @@
         <v>224</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="G82" s="5">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>226</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>902</v>
+        <v>867</v>
       </c>
     </row>
     <row r="83" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7604,7 +7604,7 @@
         <v>227</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="G83" s="5">
         <v>8</v>
@@ -7619,7 +7619,7 @@
         <v>229</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>903</v>
+        <v>868</v>
       </c>
     </row>
     <row r="84" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7633,7 +7633,7 @@
         <v>230</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="G84" s="5">
         <v>9</v>
@@ -7648,7 +7648,7 @@
         <v>232</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>904</v>
+        <v>869</v>
       </c>
     </row>
     <row r="85" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7662,7 +7662,7 @@
         <v>233</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="G85" s="5">
         <v>10</v>
@@ -7677,7 +7677,7 @@
         <v>235</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>905</v>
+        <v>870</v>
       </c>
     </row>
     <row r="86" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7691,7 +7691,7 @@
         <v>236</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="G86" s="5">
         <v>11</v>
@@ -7706,7 +7706,7 @@
         <v>238</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>906</v>
+        <v>871</v>
       </c>
     </row>
     <row r="87" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7720,7 +7720,7 @@
         <v>239</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="G87" s="5">
         <v>12</v>
@@ -7735,7 +7735,7 @@
         <v>241</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>907</v>
+        <v>872</v>
       </c>
     </row>
     <row r="88" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7749,7 +7749,7 @@
         <v>242</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="G88" s="5">
         <v>13</v>
@@ -7764,7 +7764,7 @@
         <v>244</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>908</v>
+        <v>873</v>
       </c>
     </row>
     <row r="89" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -7778,7 +7778,7 @@
         <v>245</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="G89" s="5">
         <v>14</v>
@@ -7793,7 +7793,7 @@
         <v>247</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>909</v>
+        <v>874</v>
       </c>
     </row>
     <row r="90" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7807,7 +7807,7 @@
         <v>248</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="G90" s="5">
         <v>15</v>
@@ -7822,7 +7822,7 @@
         <v>250</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>910</v>
+        <v>875</v>
       </c>
     </row>
     <row r="91" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7837,7 +7837,7 @@
         <v>251</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="G91" s="5">
         <f>G90+1</f>
@@ -7853,7 +7853,7 @@
         <v>253</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>911</v>
+        <v>876</v>
       </c>
     </row>
     <row r="92" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7868,7 +7868,7 @@
         <v>254</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="G92" s="5">
         <f t="shared" ref="G92:G110" si="5">G91+1</f>
@@ -7884,7 +7884,7 @@
         <v>256</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>912</v>
+        <v>877</v>
       </c>
     </row>
     <row r="93" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7899,7 +7899,7 @@
         <v>257</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="G93" s="5">
         <f t="shared" si="5"/>
@@ -7915,7 +7915,7 @@
         <v>259</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>913</v>
+        <v>878</v>
       </c>
     </row>
     <row r="94" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7930,7 +7930,7 @@
         <v>260</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="G94" s="5">
         <f t="shared" si="5"/>
@@ -7946,7 +7946,7 @@
         <v>262</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>914</v>
+        <v>879</v>
       </c>
     </row>
     <row r="95" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7961,7 +7961,7 @@
         <v>263</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="G95" s="5">
         <f t="shared" si="5"/>
@@ -7977,7 +7977,7 @@
         <v>265</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>915</v>
+        <v>880</v>
       </c>
     </row>
     <row r="96" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -7992,7 +7992,7 @@
         <v>266</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="G96" s="5">
         <f t="shared" si="5"/>
@@ -8008,7 +8008,7 @@
         <v>268</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>916</v>
+        <v>881</v>
       </c>
     </row>
     <row r="97" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8023,7 +8023,7 @@
         <v>269</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="G97" s="5">
         <f t="shared" si="5"/>
@@ -8039,7 +8039,7 @@
         <v>271</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>917</v>
+        <v>882</v>
       </c>
     </row>
     <row r="98" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8054,7 +8054,7 @@
         <v>272</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="G98" s="5">
         <f t="shared" si="5"/>
@@ -8070,7 +8070,7 @@
         <v>274</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>918</v>
+        <v>883</v>
       </c>
     </row>
     <row r="99" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8085,7 +8085,7 @@
         <v>275</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="G99" s="5">
         <f t="shared" si="5"/>
@@ -8101,7 +8101,7 @@
         <v>277</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>919</v>
+        <v>884</v>
       </c>
     </row>
     <row r="100" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8116,7 +8116,7 @@
         <v>278</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="G100" s="5">
         <f t="shared" si="5"/>
@@ -8132,7 +8132,7 @@
         <v>280</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>920</v>
+        <v>885</v>
       </c>
     </row>
     <row r="101" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8147,7 +8147,7 @@
         <v>281</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="G101" s="5">
         <f t="shared" si="5"/>
@@ -8163,7 +8163,7 @@
         <v>283</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>921</v>
+        <v>886</v>
       </c>
     </row>
     <row r="102" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8178,7 +8178,7 @@
         <v>284</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="G102" s="5">
         <f t="shared" si="5"/>
@@ -8194,7 +8194,7 @@
         <v>286</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>922</v>
+        <v>887</v>
       </c>
     </row>
     <row r="103" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8209,7 +8209,7 @@
         <v>287</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="G103" s="5">
         <f t="shared" si="5"/>
@@ -8225,7 +8225,7 @@
         <v>289</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>923</v>
+        <v>888</v>
       </c>
     </row>
     <row r="104" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8240,7 +8240,7 @@
         <v>290</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="G104" s="5">
         <f t="shared" si="5"/>
@@ -8256,7 +8256,7 @@
         <v>292</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>924</v>
+        <v>889</v>
       </c>
     </row>
     <row r="105" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8271,7 +8271,7 @@
         <v>293</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="G105" s="5">
         <f t="shared" si="5"/>
@@ -8287,7 +8287,7 @@
         <v>295</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>925</v>
+        <v>890</v>
       </c>
     </row>
     <row r="106" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8302,7 +8302,7 @@
         <v>296</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="G106" s="5">
         <f t="shared" si="5"/>
@@ -8318,7 +8318,7 @@
         <v>298</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>926</v>
+        <v>891</v>
       </c>
     </row>
     <row r="107" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8333,7 +8333,7 @@
         <v>299</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="G107" s="5">
         <f t="shared" si="5"/>
@@ -8349,7 +8349,7 @@
         <v>301</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>927</v>
+        <v>892</v>
       </c>
     </row>
     <row r="108" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8364,7 +8364,7 @@
         <v>302</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="G108" s="5">
         <f t="shared" si="5"/>
@@ -8380,7 +8380,7 @@
         <v>304</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>928</v>
+        <v>893</v>
       </c>
     </row>
     <row r="109" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8395,7 +8395,7 @@
         <v>305</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="G109" s="5">
         <f t="shared" si="5"/>
@@ -8411,7 +8411,7 @@
         <v>307</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>929</v>
+        <v>894</v>
       </c>
     </row>
     <row r="110" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -8426,7 +8426,7 @@
         <v>308</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="G110" s="5">
         <f t="shared" si="5"/>
@@ -8442,7 +8442,7 @@
         <v>310</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>930</v>
+        <v>895</v>
       </c>
     </row>
     <row r="111" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -8471,7 +8471,7 @@
         <v>313</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>931</v>
+        <v>896</v>
       </c>
       <c r="L111" s="8"/>
     </row>
@@ -8486,7 +8486,7 @@
         <v>314</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="G112" s="5">
         <v>2</v>
@@ -8501,7 +8501,7 @@
         <v>316</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>932</v>
+        <v>897</v>
       </c>
       <c r="L112" s="8"/>
     </row>
@@ -8516,7 +8516,7 @@
         <v>317</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="G113" s="5">
         <v>3</v>
@@ -8531,7 +8531,7 @@
         <v>319</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>933</v>
+        <v>898</v>
       </c>
       <c r="L113" s="8"/>
     </row>
@@ -8546,7 +8546,7 @@
         <v>320</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="G114" s="5">
         <v>4</v>
@@ -8561,7 +8561,7 @@
         <v>322</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>934</v>
+        <v>899</v>
       </c>
       <c r="L114" s="8"/>
     </row>
@@ -8576,7 +8576,7 @@
         <v>323</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="G115" s="5">
         <v>5</v>
@@ -8591,7 +8591,7 @@
         <v>325</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>935</v>
+        <v>900</v>
       </c>
       <c r="L115" s="8"/>
     </row>
@@ -8606,7 +8606,7 @@
         <v>326</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="G116" s="5">
         <v>6</v>
@@ -8621,7 +8621,7 @@
         <v>328</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>936</v>
+        <v>901</v>
       </c>
       <c r="L116" s="8"/>
     </row>
@@ -8651,7 +8651,7 @@
         <v>331</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>937</v>
+        <v>902</v>
       </c>
       <c r="L117" s="8"/>
     </row>
@@ -8681,7 +8681,7 @@
         <v>334</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>938</v>
+        <v>903</v>
       </c>
       <c r="L118" s="8"/>
     </row>
@@ -8711,7 +8711,7 @@
         <v>337</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>939</v>
+        <v>904</v>
       </c>
       <c r="L119" s="8"/>
     </row>
@@ -8741,7 +8741,7 @@
         <v>340</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>940</v>
+        <v>905</v>
       </c>
       <c r="L120" s="8"/>
     </row>
@@ -8756,7 +8756,7 @@
         <v>341</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="G121" s="5">
         <v>11</v>
@@ -8771,7 +8771,7 @@
         <v>343</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>941</v>
+        <v>906</v>
       </c>
       <c r="L121" s="8"/>
     </row>
@@ -8801,7 +8801,7 @@
         <v>346</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>942</v>
+        <v>907</v>
       </c>
       <c r="L122" s="8"/>
     </row>
@@ -8816,7 +8816,7 @@
         <v>347</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="G123" s="5">
         <v>13</v>
@@ -8831,7 +8831,7 @@
         <v>349</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>943</v>
+        <v>908</v>
       </c>
       <c r="L123" s="8"/>
     </row>
@@ -8861,7 +8861,7 @@
         <v>352</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>944</v>
+        <v>909</v>
       </c>
       <c r="L124" s="8"/>
     </row>
@@ -8876,7 +8876,7 @@
         <v>353</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="G125" s="5">
         <v>15</v>
@@ -8891,7 +8891,7 @@
         <v>355</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>945</v>
+        <v>910</v>
       </c>
       <c r="L125" s="8"/>
     </row>
@@ -8907,7 +8907,7 @@
         <v>356</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="G126" s="5">
         <f>G125+1</f>
@@ -8923,7 +8923,7 @@
         <v>358</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>946</v>
+        <v>911</v>
       </c>
       <c r="L126" s="8"/>
     </row>
@@ -8955,7 +8955,7 @@
         <v>361</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>947</v>
+        <v>912</v>
       </c>
       <c r="L127" s="8"/>
     </row>
@@ -8971,7 +8971,7 @@
         <v>362</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="G128" s="5">
         <f t="shared" si="7"/>
@@ -8987,7 +8987,7 @@
         <v>364</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>948</v>
+        <v>913</v>
       </c>
       <c r="L128" s="8"/>
     </row>
@@ -9003,7 +9003,7 @@
         <v>365</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="G129" s="5">
         <f t="shared" si="7"/>
@@ -9019,7 +9019,7 @@
         <v>367</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>949</v>
+        <v>914</v>
       </c>
       <c r="L129" s="8"/>
     </row>
@@ -9051,7 +9051,7 @@
         <v>370</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>950</v>
+        <v>915</v>
       </c>
       <c r="L130" s="8"/>
     </row>
@@ -9083,7 +9083,7 @@
         <v>373</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>951</v>
+        <v>916</v>
       </c>
       <c r="L131" s="8"/>
     </row>
@@ -9099,7 +9099,7 @@
         <v>374</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="G132" s="5">
         <f t="shared" si="7"/>
@@ -9115,7 +9115,7 @@
         <v>376</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>952</v>
+        <v>917</v>
       </c>
       <c r="L132" s="8"/>
     </row>
@@ -9131,7 +9131,7 @@
         <v>377</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="G133" s="5">
         <f t="shared" si="7"/>
@@ -9147,7 +9147,7 @@
         <v>379</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>953</v>
+        <v>918</v>
       </c>
       <c r="L133" s="8"/>
     </row>
@@ -9163,7 +9163,7 @@
         <v>380</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="G134" s="5">
         <f t="shared" si="7"/>
@@ -9179,7 +9179,7 @@
         <v>382</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>954</v>
+        <v>919</v>
       </c>
       <c r="L134" s="8"/>
     </row>
@@ -9195,7 +9195,7 @@
         <v>383</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="G135" s="5">
         <f t="shared" si="7"/>
@@ -9211,7 +9211,7 @@
         <v>385</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="L135" s="8"/>
     </row>
@@ -9227,7 +9227,7 @@
         <v>386</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="G136" s="5">
         <f t="shared" si="7"/>
@@ -9243,7 +9243,7 @@
         <v>388</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>956</v>
+        <v>921</v>
       </c>
       <c r="L136" s="8"/>
     </row>
@@ -9275,7 +9275,7 @@
         <v>391</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>957</v>
+        <v>922</v>
       </c>
       <c r="L137" s="8"/>
     </row>
@@ -9291,7 +9291,7 @@
         <v>392</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="G138" s="5">
         <f t="shared" si="7"/>
@@ -9307,7 +9307,7 @@
         <v>394</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>958</v>
+        <v>923</v>
       </c>
       <c r="L138" s="8"/>
     </row>
@@ -9323,7 +9323,7 @@
         <v>395</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="G139" s="5">
         <f t="shared" si="7"/>
@@ -9339,7 +9339,7 @@
         <v>397</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>959</v>
+        <v>924</v>
       </c>
       <c r="L139" s="8"/>
     </row>
@@ -9371,7 +9371,7 @@
         <v>400</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>960</v>
+        <v>925</v>
       </c>
       <c r="L140" s="8"/>
     </row>
@@ -9387,7 +9387,7 @@
         <v>401</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="G141" s="5">
         <f t="shared" si="7"/>
@@ -9403,7 +9403,7 @@
         <v>403</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>961</v>
+        <v>926</v>
       </c>
       <c r="L141" s="8"/>
     </row>
@@ -9435,7 +9435,7 @@
         <v>406</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>962</v>
+        <v>927</v>
       </c>
       <c r="L142" s="8"/>
     </row>
@@ -9451,7 +9451,7 @@
         <v>407</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="G143" s="5">
         <f t="shared" si="7"/>
@@ -9467,7 +9467,7 @@
         <v>409</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
       <c r="L143" s="8"/>
     </row>
@@ -9483,7 +9483,7 @@
         <v>410</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="G144" s="5">
         <f t="shared" si="7"/>
@@ -9499,7 +9499,7 @@
         <v>412</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>964</v>
+        <v>929</v>
       </c>
       <c r="L144" s="8"/>
     </row>
@@ -9515,7 +9515,7 @@
         <v>413</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="G145" s="5">
         <f t="shared" si="7"/>
@@ -9531,7 +9531,7 @@
         <v>415</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>965</v>
+        <v>930</v>
       </c>
       <c r="L145" s="8"/>
     </row>
@@ -9546,7 +9546,7 @@
         <v>416</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="G146" s="5">
         <v>1</v>
@@ -9561,7 +9561,7 @@
         <v>418</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>966</v>
+        <v>931</v>
       </c>
     </row>
     <row r="147" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9575,7 +9575,7 @@
         <v>419</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="G147" s="5">
         <v>2</v>
@@ -9590,7 +9590,7 @@
         <v>421</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>967</v>
+        <v>932</v>
       </c>
     </row>
     <row r="148" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9604,7 +9604,7 @@
         <v>422</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="G148" s="5">
         <v>3</v>
@@ -9619,7 +9619,7 @@
         <v>424</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>968</v>
+        <v>933</v>
       </c>
     </row>
     <row r="149" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9633,7 +9633,7 @@
         <v>425</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="G149" s="5">
         <v>4</v>
@@ -9648,7 +9648,7 @@
         <v>427</v>
       </c>
       <c r="K149" s="7" t="s">
-        <v>969</v>
+        <v>934</v>
       </c>
     </row>
     <row r="150" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9662,7 +9662,7 @@
         <v>428</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="G150" s="5">
         <v>5</v>
@@ -9677,7 +9677,7 @@
         <v>430</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>970</v>
+        <v>935</v>
       </c>
     </row>
     <row r="151" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9691,7 +9691,7 @@
         <v>431</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="G151" s="5">
         <v>6</v>
@@ -9706,7 +9706,7 @@
         <v>433</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>971</v>
+        <v>936</v>
       </c>
     </row>
     <row r="152" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9720,7 +9720,7 @@
         <v>434</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="G152" s="5">
         <v>7</v>
@@ -9735,7 +9735,7 @@
         <v>436</v>
       </c>
       <c r="K152" s="7" t="s">
-        <v>972</v>
+        <v>937</v>
       </c>
     </row>
     <row r="153" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9749,7 +9749,7 @@
         <v>437</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="G153" s="5">
         <v>8</v>
@@ -9764,7 +9764,7 @@
         <v>439</v>
       </c>
       <c r="K153" s="7" t="s">
-        <v>973</v>
+        <v>938</v>
       </c>
     </row>
     <row r="154" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9778,7 +9778,7 @@
         <v>440</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="G154" s="5">
         <v>9</v>
@@ -9793,7 +9793,7 @@
         <v>442</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>974</v>
+        <v>939</v>
       </c>
     </row>
     <row r="155" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9807,7 +9807,7 @@
         <v>443</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="G155" s="5">
         <v>10</v>
@@ -9822,7 +9822,7 @@
         <v>445</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>975</v>
+        <v>940</v>
       </c>
     </row>
     <row r="156" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9836,7 +9836,7 @@
         <v>446</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="G156" s="5">
         <v>11</v>
@@ -9851,7 +9851,7 @@
         <v>448</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>976</v>
+        <v>941</v>
       </c>
     </row>
     <row r="157" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -9865,7 +9865,7 @@
         <v>449</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="G157" s="5">
         <v>12</v>
@@ -9880,7 +9880,7 @@
         <v>451</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>977</v>
+        <v>942</v>
       </c>
     </row>
     <row r="158" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9894,7 +9894,7 @@
         <v>452</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="G158" s="5">
         <v>13</v>
@@ -9909,7 +9909,7 @@
         <v>454</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>978</v>
+        <v>943</v>
       </c>
     </row>
     <row r="159" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -9923,7 +9923,7 @@
         <v>455</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="G159" s="5">
         <v>14</v>
@@ -9938,7 +9938,7 @@
         <v>457</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>979</v>
+        <v>944</v>
       </c>
     </row>
     <row r="160" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -9952,7 +9952,7 @@
         <v>458</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="G160" s="5">
         <v>15</v>
@@ -9967,7 +9967,7 @@
         <v>460</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>980</v>
+        <v>945</v>
       </c>
     </row>
     <row r="161" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -9982,7 +9982,7 @@
         <v>461</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="G161" s="5">
         <f>G160+1</f>
@@ -9998,7 +9998,7 @@
         <v>463</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>981</v>
+        <v>946</v>
       </c>
     </row>
     <row r="162" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10013,7 +10013,7 @@
         <v>464</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="G162" s="5">
         <f t="shared" ref="G162:G180" si="9">G161+1</f>
@@ -10029,7 +10029,7 @@
         <v>466</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>982</v>
+        <v>947</v>
       </c>
     </row>
     <row r="163" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10044,7 +10044,7 @@
         <v>467</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="G163" s="5">
         <f t="shared" si="9"/>
@@ -10060,7 +10060,7 @@
         <v>469</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>983</v>
+        <v>948</v>
       </c>
     </row>
     <row r="164" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10075,7 +10075,7 @@
         <v>470</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="G164" s="5">
         <f t="shared" si="9"/>
@@ -10091,7 +10091,7 @@
         <v>472</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>984</v>
+        <v>949</v>
       </c>
     </row>
     <row r="165" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10106,7 +10106,7 @@
         <v>473</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="G165" s="5">
         <f t="shared" si="9"/>
@@ -10122,7 +10122,7 @@
         <v>475</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>985</v>
+        <v>950</v>
       </c>
     </row>
     <row r="166" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10137,7 +10137,7 @@
         <v>476</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="G166" s="5">
         <f t="shared" si="9"/>
@@ -10153,7 +10153,7 @@
         <v>478</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>986</v>
+        <v>951</v>
       </c>
     </row>
     <row r="167" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10168,7 +10168,7 @@
         <v>479</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="G167" s="5">
         <f t="shared" si="9"/>
@@ -10184,7 +10184,7 @@
         <v>481</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>987</v>
+        <v>952</v>
       </c>
     </row>
     <row r="168" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10199,7 +10199,7 @@
         <v>482</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="G168" s="5">
         <f t="shared" si="9"/>
@@ -10215,7 +10215,7 @@
         <v>484</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>988</v>
+        <v>953</v>
       </c>
     </row>
     <row r="169" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10230,7 +10230,7 @@
         <v>485</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="G169" s="5">
         <f t="shared" si="9"/>
@@ -10246,7 +10246,7 @@
         <v>487</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>989</v>
+        <v>954</v>
       </c>
     </row>
     <row r="170" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10261,7 +10261,7 @@
         <v>488</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="G170" s="5">
         <f t="shared" si="9"/>
@@ -10277,7 +10277,7 @@
         <v>490</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>990</v>
+        <v>955</v>
       </c>
     </row>
     <row r="171" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10292,7 +10292,7 @@
         <v>491</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="G171" s="5">
         <f t="shared" si="9"/>
@@ -10308,7 +10308,7 @@
         <v>493</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>991</v>
+        <v>956</v>
       </c>
     </row>
     <row r="172" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10323,7 +10323,7 @@
         <v>494</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="G172" s="5">
         <f t="shared" si="9"/>
@@ -10339,7 +10339,7 @@
         <v>496</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>992</v>
+        <v>957</v>
       </c>
     </row>
     <row r="173" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10354,7 +10354,7 @@
         <v>497</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="G173" s="5">
         <f t="shared" si="9"/>
@@ -10370,7 +10370,7 @@
         <v>499</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>993</v>
+        <v>958</v>
       </c>
     </row>
     <row r="174" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10385,7 +10385,7 @@
         <v>500</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="G174" s="5">
         <f t="shared" si="9"/>
@@ -10401,7 +10401,7 @@
         <v>502</v>
       </c>
       <c r="K174" s="7" t="s">
-        <v>994</v>
+        <v>959</v>
       </c>
     </row>
     <row r="175" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10416,7 +10416,7 @@
         <v>503</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="G175" s="5">
         <f t="shared" si="9"/>
@@ -10432,7 +10432,7 @@
         <v>505</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>995</v>
+        <v>960</v>
       </c>
     </row>
     <row r="176" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10447,7 +10447,7 @@
         <v>506</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="G176" s="5">
         <f t="shared" si="9"/>
@@ -10463,7 +10463,7 @@
         <v>508</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>996</v>
+        <v>961</v>
       </c>
     </row>
     <row r="177" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10478,7 +10478,7 @@
         <v>509</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="G177" s="5">
         <f t="shared" si="9"/>
@@ -10494,7 +10494,7 @@
         <v>511</v>
       </c>
       <c r="K177" s="7" t="s">
-        <v>997</v>
+        <v>962</v>
       </c>
     </row>
     <row r="178" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10509,7 +10509,7 @@
         <v>512</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="G178" s="5">
         <f t="shared" si="9"/>
@@ -10525,7 +10525,7 @@
         <v>514</v>
       </c>
       <c r="K178" s="7" t="s">
-        <v>998</v>
+        <v>963</v>
       </c>
     </row>
     <row r="179" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10540,7 +10540,7 @@
         <v>515</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="G179" s="5">
         <f t="shared" si="9"/>
@@ -10556,7 +10556,7 @@
         <v>517</v>
       </c>
       <c r="K179" s="7" t="s">
-        <v>999</v>
+        <v>964</v>
       </c>
     </row>
     <row r="180" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10571,7 +10571,7 @@
         <v>518</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="G180" s="5">
         <f t="shared" si="9"/>
@@ -10587,7 +10587,7 @@
         <v>520</v>
       </c>
       <c r="K180" s="7" t="s">
-        <v>1000</v>
+        <v>965</v>
       </c>
     </row>
     <row r="181" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10601,7 +10601,7 @@
         <v>521</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>618</v>
+        <v>1001</v>
       </c>
       <c r="G181" s="5">
         <v>1</v>
@@ -10617,7 +10617,7 @@
         <v>生命上限提升+1%,眩晕抵抗概率+1%</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>1001</v>
+        <v>966</v>
       </c>
     </row>
     <row r="182" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10631,7 +10631,7 @@
         <v>523</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>619</v>
+        <v>1002</v>
       </c>
       <c r="G182" s="5">
         <v>2</v>
@@ -10647,7 +10647,7 @@
         <v>生命上限提升+2%,眩晕抵抗概率+2%</v>
       </c>
       <c r="K182" s="7" t="s">
-        <v>1002</v>
+        <v>967</v>
       </c>
     </row>
     <row r="183" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10661,7 +10661,7 @@
         <v>525</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>799</v>
+        <v>1003</v>
       </c>
       <c r="G183" s="5">
         <v>3</v>
@@ -10677,7 +10677,7 @@
         <v>生命上限提升+3%,眩晕抵抗概率+3%</v>
       </c>
       <c r="K183" s="7" t="s">
-        <v>1003</v>
+        <v>968</v>
       </c>
     </row>
     <row r="184" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10691,7 +10691,7 @@
         <v>527</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>800</v>
+        <v>1004</v>
       </c>
       <c r="G184" s="5">
         <v>4</v>
@@ -10707,7 +10707,7 @@
         <v>生命上限提升+4%,眩晕抵抗概率+4%</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>1004</v>
+        <v>969</v>
       </c>
     </row>
     <row r="185" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10721,7 +10721,7 @@
         <v>529</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>801</v>
+        <v>1005</v>
       </c>
       <c r="G185" s="5">
         <v>5</v>
@@ -10737,7 +10737,7 @@
         <v>生命上限提升+5%,眩晕抵抗概率+5%</v>
       </c>
       <c r="K185" s="7" t="s">
-        <v>1005</v>
+        <v>970</v>
       </c>
     </row>
     <row r="186" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10751,7 +10751,7 @@
         <v>531</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>802</v>
+        <v>1006</v>
       </c>
       <c r="G186" s="5">
         <v>6</v>
@@ -10767,7 +10767,7 @@
         <v>生命上限提升+6%,眩晕抵抗概率+6%</v>
       </c>
       <c r="K186" s="7" t="s">
-        <v>1006</v>
+        <v>971</v>
       </c>
     </row>
     <row r="187" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10781,7 +10781,7 @@
         <v>533</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>803</v>
+        <v>1007</v>
       </c>
       <c r="G187" s="5">
         <v>7</v>
@@ -10797,7 +10797,7 @@
         <v>生命上限提升+7%,眩晕抵抗概率+7%</v>
       </c>
       <c r="K187" s="7" t="s">
-        <v>1007</v>
+        <v>972</v>
       </c>
     </row>
     <row r="188" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10811,7 +10811,7 @@
         <v>535</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>620</v>
+        <v>1008</v>
       </c>
       <c r="G188" s="5">
         <v>8</v>
@@ -10827,7 +10827,7 @@
         <v>生命上限提升+8%,眩晕抵抗概率+8%</v>
       </c>
       <c r="K188" s="7" t="s">
-        <v>1008</v>
+        <v>973</v>
       </c>
     </row>
     <row r="189" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10841,7 +10841,7 @@
         <v>537</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>804</v>
+        <v>1009</v>
       </c>
       <c r="G189" s="5">
         <v>9</v>
@@ -10857,7 +10857,7 @@
         <v>生命上限提升+9%,眩晕抵抗概率+9%</v>
       </c>
       <c r="K189" s="7" t="s">
-        <v>1009</v>
+        <v>974</v>
       </c>
     </row>
     <row r="190" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10871,7 +10871,7 @@
         <v>539</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>621</v>
+        <v>1010</v>
       </c>
       <c r="G190" s="5">
         <v>10</v>
@@ -10887,7 +10887,7 @@
         <v>生命上限提升+10%,眩晕抵抗概率+10%</v>
       </c>
       <c r="K190" s="7" t="s">
-        <v>1010</v>
+        <v>975</v>
       </c>
     </row>
     <row r="191" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10901,7 +10901,7 @@
         <v>541</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>805</v>
+        <v>1011</v>
       </c>
       <c r="G191" s="5">
         <v>11</v>
@@ -10917,7 +10917,7 @@
         <v>生命上限提升+11%,眩晕抵抗概率+11%</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>1011</v>
+        <v>976</v>
       </c>
     </row>
     <row r="192" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -10931,7 +10931,7 @@
         <v>543</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>806</v>
+        <v>1012</v>
       </c>
       <c r="G192" s="5">
         <v>12</v>
@@ -10947,7 +10947,7 @@
         <v>生命上限提升+12%,眩晕抵抗概率+12%</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>1012</v>
+        <v>977</v>
       </c>
     </row>
     <row r="193" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10961,7 +10961,7 @@
         <v>545</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>807</v>
+        <v>1013</v>
       </c>
       <c r="G193" s="5">
         <v>13</v>
@@ -10977,7 +10977,7 @@
         <v>生命上限提升+13%,眩晕抵抗概率+13%</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>1013</v>
+        <v>978</v>
       </c>
     </row>
     <row r="194" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -10991,7 +10991,7 @@
         <v>547</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>808</v>
+        <v>1014</v>
       </c>
       <c r="G194" s="5">
         <v>14</v>
@@ -11007,7 +11007,7 @@
         <v>生命上限提升+14%,眩晕抵抗概率+14%</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
     </row>
     <row r="195" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11021,7 +11021,7 @@
         <v>549</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>809</v>
+        <v>1015</v>
       </c>
       <c r="G195" s="5">
         <v>15</v>
@@ -11037,7 +11037,7 @@
         <v>生命上限提升+15%,眩晕抵抗概率+15%</v>
       </c>
       <c r="K195" s="7" t="s">
-        <v>1015</v>
+        <v>980</v>
       </c>
     </row>
     <row r="196" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11052,7 +11052,7 @@
         <v>551</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>622</v>
+        <v>1016</v>
       </c>
       <c r="G196" s="5">
         <f>G195+1</f>
@@ -11069,7 +11069,7 @@
         <v>生命上限提升+16%,眩晕抵抗概率+16%</v>
       </c>
       <c r="K196" s="7" t="s">
-        <v>1016</v>
+        <v>981</v>
       </c>
     </row>
     <row r="197" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11084,7 +11084,7 @@
         <v>553</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>810</v>
+        <v>1017</v>
       </c>
       <c r="G197" s="5">
         <f t="shared" ref="G197:G210" si="12">G196+1</f>
@@ -11101,7 +11101,7 @@
         <v>生命上限提升+17%,眩晕抵抗概率+17%</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>1017</v>
+        <v>982</v>
       </c>
     </row>
     <row r="198" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11116,7 +11116,7 @@
         <v>555</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>811</v>
+        <v>1018</v>
       </c>
       <c r="G198" s="5">
         <f t="shared" si="12"/>
@@ -11133,7 +11133,7 @@
         <v>生命上限提升+18%,眩晕抵抗概率+18%</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>1018</v>
+        <v>983</v>
       </c>
     </row>
     <row r="199" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11148,7 +11148,7 @@
         <v>557</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>812</v>
+        <v>1019</v>
       </c>
       <c r="G199" s="5">
         <f t="shared" si="12"/>
@@ -11165,7 +11165,7 @@
         <v>生命上限提升+19%,眩晕抵抗概率+19%</v>
       </c>
       <c r="K199" s="7" t="s">
-        <v>1019</v>
+        <v>984</v>
       </c>
     </row>
     <row r="200" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11180,7 +11180,7 @@
         <v>559</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>813</v>
+        <v>1020</v>
       </c>
       <c r="G200" s="5">
         <f t="shared" si="12"/>
@@ -11197,7 +11197,7 @@
         <v>生命上限提升+20%,眩晕抵抗概率+20%</v>
       </c>
       <c r="K200" s="7" t="s">
-        <v>1020</v>
+        <v>985</v>
       </c>
     </row>
     <row r="201" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11212,7 +11212,7 @@
         <v>561</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>814</v>
+        <v>1021</v>
       </c>
       <c r="G201" s="5">
         <f t="shared" si="12"/>
@@ -11229,7 +11229,7 @@
         <v>生命上限提升+21%,眩晕抵抗概率+21%</v>
       </c>
       <c r="K201" s="7" t="s">
-        <v>1021</v>
+        <v>986</v>
       </c>
     </row>
     <row r="202" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11244,7 +11244,7 @@
         <v>563</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>623</v>
+        <v>1022</v>
       </c>
       <c r="G202" s="5">
         <f t="shared" si="12"/>
@@ -11261,7 +11261,7 @@
         <v>生命上限提升+22%,眩晕抵抗概率+22%</v>
       </c>
       <c r="K202" s="7" t="s">
-        <v>1022</v>
+        <v>987</v>
       </c>
     </row>
     <row r="203" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11276,7 +11276,7 @@
         <v>565</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>815</v>
+        <v>1023</v>
       </c>
       <c r="G203" s="5">
         <f t="shared" si="12"/>
@@ -11293,7 +11293,7 @@
         <v>生命上限提升+23%,眩晕抵抗概率+23%</v>
       </c>
       <c r="K203" s="7" t="s">
-        <v>1023</v>
+        <v>988</v>
       </c>
     </row>
     <row r="204" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11308,7 +11308,7 @@
         <v>567</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>624</v>
+        <v>1024</v>
       </c>
       <c r="G204" s="5">
         <f t="shared" si="12"/>
@@ -11325,7 +11325,7 @@
         <v>生命上限提升+24%,眩晕抵抗概率+24%</v>
       </c>
       <c r="K204" s="7" t="s">
-        <v>1024</v>
+        <v>989</v>
       </c>
     </row>
     <row r="205" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11340,7 +11340,7 @@
         <v>569</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>625</v>
+        <v>1025</v>
       </c>
       <c r="G205" s="5">
         <f t="shared" si="12"/>
@@ -11357,7 +11357,7 @@
         <v>生命上限提升+25%,眩晕抵抗概率+25%</v>
       </c>
       <c r="K205" s="7" t="s">
-        <v>1025</v>
+        <v>990</v>
       </c>
     </row>
     <row r="206" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11372,7 +11372,7 @@
         <v>571</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>816</v>
+        <v>1026</v>
       </c>
       <c r="G206" s="5">
         <f t="shared" si="12"/>
@@ -11389,7 +11389,7 @@
         <v>生命上限提升+26%,眩晕抵抗概率+26%</v>
       </c>
       <c r="K206" s="7" t="s">
-        <v>1026</v>
+        <v>991</v>
       </c>
     </row>
     <row r="207" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11404,7 +11404,7 @@
         <v>573</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>817</v>
+        <v>1027</v>
       </c>
       <c r="G207" s="5">
         <f t="shared" si="12"/>
@@ -11421,7 +11421,7 @@
         <v>生命上限提升+27%,眩晕抵抗概率+27%</v>
       </c>
       <c r="K207" s="7" t="s">
-        <v>1027</v>
+        <v>992</v>
       </c>
     </row>
     <row r="208" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11436,7 +11436,7 @@
         <v>575</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>626</v>
+        <v>1028</v>
       </c>
       <c r="G208" s="5">
         <f t="shared" si="12"/>
@@ -11453,7 +11453,7 @@
         <v>生命上限提升+28%,眩晕抵抗概率+28%</v>
       </c>
       <c r="K208" s="7" t="s">
-        <v>1028</v>
+        <v>993</v>
       </c>
     </row>
     <row r="209" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11468,7 +11468,7 @@
         <v>577</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>818</v>
+        <v>1029</v>
       </c>
       <c r="G209" s="5">
         <f t="shared" si="12"/>
@@ -11485,7 +11485,7 @@
         <v>生命上限提升+29%,眩晕抵抗概率+29%</v>
       </c>
       <c r="K209" s="7" t="s">
-        <v>1029</v>
+        <v>994</v>
       </c>
     </row>
     <row r="210" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11500,7 +11500,7 @@
         <v>579</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>819</v>
+        <v>1030</v>
       </c>
       <c r="G210" s="5">
         <f t="shared" si="12"/>
@@ -11517,7 +11517,7 @@
         <v>生命上限提升+30%,眩晕抵抗概率+30%</v>
       </c>
       <c r="K210" s="7" t="s">
-        <v>1030</v>
+        <v>995</v>
       </c>
     </row>
     <row r="211" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11532,7 +11532,7 @@
         <v>581</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>820</v>
+        <v>1031</v>
       </c>
       <c r="G211" s="9">
         <f t="shared" ref="G211:G215" si="16">G210+1</f>
@@ -11549,7 +11549,7 @@
         <v>生命上限提升+31%,眩晕抵抗概率+31%</v>
       </c>
       <c r="K211" s="7" t="s">
-        <v>1031</v>
+        <v>996</v>
       </c>
     </row>
     <row r="212" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11564,7 +11564,7 @@
         <v>583</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>821</v>
+        <v>1032</v>
       </c>
       <c r="G212" s="9">
         <f t="shared" si="16"/>
@@ -11581,7 +11581,7 @@
         <v>生命上限提升+32%,眩晕抵抗概率+32%</v>
       </c>
       <c r="K212" s="7" t="s">
-        <v>1032</v>
+        <v>997</v>
       </c>
     </row>
     <row r="213" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11597,7 +11597,7 @@
         <v>585</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>822</v>
+        <v>1033</v>
       </c>
       <c r="G213" s="9">
         <f t="shared" si="16"/>
@@ -11614,7 +11614,7 @@
         <v>生命上限提升+33%,眩晕抵抗概率+33%</v>
       </c>
       <c r="K213" s="7" t="s">
-        <v>1033</v>
+        <v>998</v>
       </c>
     </row>
     <row r="214" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11629,7 +11629,7 @@
         <v>587</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>823</v>
+        <v>1034</v>
       </c>
       <c r="G214" s="9">
         <f t="shared" si="16"/>
@@ -11646,7 +11646,7 @@
         <v>生命上限提升+34%,眩晕抵抗概率+34%</v>
       </c>
       <c r="K214" s="7" t="s">
-        <v>1034</v>
+        <v>999</v>
       </c>
     </row>
     <row r="215" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -11661,7 +11661,7 @@
         <v>589</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>627</v>
+        <v>1035</v>
       </c>
       <c r="G215" s="9">
         <f t="shared" si="16"/>
@@ -11678,7 +11678,7 @@
         <v>生命上限提升+35%,眩晕抵抗概率+35%</v>
       </c>
       <c r="K215" s="7" t="s">
-        <v>1035</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/LifeShieldConfig.xlsx
+++ b/Excel/LifeShieldConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7E7324-E134-4CC7-B636-740C94CB6EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD7C36-02FF-44B7-B097-8AF1AF8CED90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LifeShieldProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="1181">
   <si>
     <t>c</t>
   </si>
@@ -2546,12 +2546,6 @@
     <t>Reduce damage from player's normal attacks by 34%</t>
   </si>
   <si>
-    <t>Reduce damage from player's normal attacks by 35%.</t>
-  </si>
-  <si>
-    <t>Reduce damage taken from player skills by 1%.</t>
-  </si>
-  <si>
     <t>Reduce damage from player skills by 2%</t>
   </si>
   <si>
@@ -2649,9 +2643,6 @@
   </si>
   <si>
     <t>Reduce damage from player skills by 34%</t>
-  </si>
-  <si>
-    <t>Reduces damage from player skills by 35%</t>
   </si>
   <si>
     <t>Reduce all damage received from players by 0.5%</t>
@@ -3212,6 +3203,504 @@
   </si>
   <si>
     <t>Life Soul Level 35</t>
+  </si>
+  <si>
+    <t>熔岩之魂36级</t>
+  </si>
+  <si>
+    <t>熔岩之魂37级</t>
+  </si>
+  <si>
+    <t>熔岩之魂38级</t>
+  </si>
+  <si>
+    <t>熔岩之魂39级</t>
+  </si>
+  <si>
+    <t>熔岩之魂40级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 36</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 37</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 38</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 39</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 40</t>
+  </si>
+  <si>
+    <t>205703;0.36</t>
+  </si>
+  <si>
+    <t>205703;0.37</t>
+  </si>
+  <si>
+    <t>205703;0.38</t>
+  </si>
+  <si>
+    <t>205703;0.39</t>
+  </si>
+  <si>
+    <t>205703;0.40</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害36%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 36%</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害37%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 37%</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害38%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 38%</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害39%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 39%</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害40%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 40%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 35%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce damage taken from player skills by 1%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>205803;0.36</t>
+  </si>
+  <si>
+    <t>降低受到玩家技能伤害36%</t>
+  </si>
+  <si>
+    <t>205803;0.37</t>
+  </si>
+  <si>
+    <t>降低受到玩家技能伤害37%</t>
+  </si>
+  <si>
+    <t>205803;0.38</t>
+  </si>
+  <si>
+    <t>降低受到玩家技能伤害38%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 36%</t>
+  </si>
+  <si>
+    <t>205803;0.39</t>
+  </si>
+  <si>
+    <t>降低受到玩家技能伤害39%</t>
+  </si>
+  <si>
+    <t>205803;0.40</t>
+  </si>
+  <si>
+    <t>降低受到玩家技能伤害40%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 37%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 35%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 38%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 39%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player skills by 40%</t>
+  </si>
+  <si>
+    <t>巨龙之魂36级</t>
+  </si>
+  <si>
+    <t>巨龙之魂37级</t>
+  </si>
+  <si>
+    <t>巨龙之魂38级</t>
+  </si>
+  <si>
+    <t>巨龙之魂39级</t>
+  </si>
+  <si>
+    <t>巨龙之魂40级</t>
+  </si>
+  <si>
+    <t>Dragon Soul Level 36</t>
+  </si>
+  <si>
+    <t>Dragon Soul Level 37</t>
+  </si>
+  <si>
+    <t>Dragon Soul Level 38</t>
+  </si>
+  <si>
+    <t>Dragon Soul Level 39</t>
+  </si>
+  <si>
+    <t>Dragon Soul Level 40</t>
+  </si>
+  <si>
+    <t>独兽之魂36级</t>
+  </si>
+  <si>
+    <t>Beast Soul Level 36</t>
+  </si>
+  <si>
+    <t>独兽之魂37级</t>
+  </si>
+  <si>
+    <t>Beast Soul Level 37</t>
+  </si>
+  <si>
+    <t>独兽之魂38级</t>
+  </si>
+  <si>
+    <t>Beast Soul Level 38</t>
+  </si>
+  <si>
+    <t>独兽之魂39级</t>
+  </si>
+  <si>
+    <t>Beast Soul Level 39</t>
+  </si>
+  <si>
+    <t>独兽之魂40级</t>
+  </si>
+  <si>
+    <t>Beast Soul Level 40</t>
+  </si>
+  <si>
+    <t>降低受到玩家全部伤害18%</t>
+  </si>
+  <si>
+    <t>降低受到玩家全部伤害19%</t>
+  </si>
+  <si>
+    <t>降低受到玩家全部伤害20%</t>
+  </si>
+  <si>
+    <t>205903;0.18</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>205903;0.185</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>205903;0.19</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>205903;0.195</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>205903;0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低受到玩家全部伤害19.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低受到玩家全部伤害18.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce the received damage from players by 18%.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce the received damage from players by 18.5%.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce the received damage from players by 19%.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce the received damage from players by 19.5%.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce the received damage from players by 20%.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>愤怒之魂36级</t>
+  </si>
+  <si>
+    <t>愤怒之魂37级</t>
+  </si>
+  <si>
+    <t>愤怒之魂38级</t>
+  </si>
+  <si>
+    <t>愤怒之魂39级</t>
+  </si>
+  <si>
+    <t>愤怒之魂40级</t>
+  </si>
+  <si>
+    <t>Anger Soul Level 36</t>
+  </si>
+  <si>
+    <t>Anger Soul Level 37</t>
+  </si>
+  <si>
+    <t>Anger Soul Level 38</t>
+  </si>
+  <si>
+    <t>Anger Soul Level 39</t>
+  </si>
+  <si>
+    <t>Anger Soul Level 40</t>
+  </si>
+  <si>
+    <t>增加对玩家暴击概率17%,降低受到玩家暴击概率18%</t>
+  </si>
+  <si>
+    <t>增加对玩家暴击概率20%,降低受到玩家暴击概率20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家暴击概率18.5%,降低受到玩家暴击概率18.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家暴击概率19%,降低受到玩家暴击概率19%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家暴击概率19.5%,降低受到玩家暴击概率19.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206003;0.2@208103;0.2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206003;0.195@208103;0.195</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206003;0.19@208103;0.19</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206003;0.185@208103;0.185</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206003;0.18@208103;0.18</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the chance of player critical hits by 18%, and reduce the chance of being hit by player critical hits by 8%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the chance of player critical hits by 18.5%, and reduce the chance of being hit by player critical hits by 18.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the chance of player critical hits by 19%, and reduce the chance of being hit by player critical hits by 19%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the chance of player critical hits by 19.5%, and reduce the chance of being hit by player critical hits by 19.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the chance of player critical hits by 20%, and reduce the chance of being hit by player critical hits by 20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱逐之魂36级</t>
+  </si>
+  <si>
+    <t>驱逐之魂37级</t>
+  </si>
+  <si>
+    <t>驱逐之魂38级</t>
+  </si>
+  <si>
+    <t>驱逐之魂39级</t>
+  </si>
+  <si>
+    <t>驱逐之魂40级</t>
+  </si>
+  <si>
+    <t>Expulsion Soul level 36</t>
+  </si>
+  <si>
+    <t>Expulsion Soul level 37</t>
+  </si>
+  <si>
+    <t>Expulsion Soul level 38</t>
+  </si>
+  <si>
+    <t>Expulsion Soul level 39</t>
+  </si>
+  <si>
+    <t>Expulsion Soul level 40</t>
+  </si>
+  <si>
+    <t>206103;0.19@208203;0.19</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206103;0.195@208203;0.195</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206103;0.20@208203;0.20</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206103;0.185@208203;0.185</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>206103;0.18@208203;0.18</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家命中概率19%,降低受到玩家命中概率19%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家命中概率19.5%,降低受到玩家命中概率19.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家命中概率20%,降低受到玩家命中概率20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家命中概率18%,降低受到玩家命中概率18%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加对玩家命中概率18.5%,降低受到玩家命中概率18.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the player's hit probability by 18%, and decrease the player's hit probability received by 18%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the player's hit probability by 18.5%, and decrease the player's hit probability received by 18.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the player's hit probability by 19%, and decrease the player's hit probability received by 19%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the player's hit probability by 19.5%, and decrease the player's hit probability received by 19.5%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase the player's hit probability by 20%, and decrease the player's hit probability received by 20%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Life Soul Level 36</t>
+  </si>
+  <si>
+    <t>Life Soul Level 37</t>
+  </si>
+  <si>
+    <t>Life Soul Level 38</t>
+  </si>
+  <si>
+    <t>Life Soul Level 39</t>
+  </si>
+  <si>
+    <t>Life Soul Level 40</t>
+  </si>
+  <si>
+    <t>100202;0.36@213103;0.36</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>100202;0.37@213103;0.37</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>100202;0.38@213103;0.38</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>100202;0.39@213103;0.39</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>100202;0.4@213103;0.4</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum HP increased by 36%, and 36% chance to resist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum HP increased by 37%, and 37% chance to resist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum HP increased by 38%, and 38% chance to resist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum HP increased by 39%, and 39% chance to resist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum HP increased by 40%, and 40% chance to resist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命之魂36级</t>
+  </si>
+  <si>
+    <t>生命之魂37级</t>
+  </si>
+  <si>
+    <t>生命之魂38级</t>
+  </si>
+  <si>
+    <t>生命之魂39级</t>
+  </si>
+  <si>
+    <t>生命之魂40级</t>
   </si>
 </sst>
 </file>
@@ -4865,7 +5354,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:K215" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:K245" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
@@ -5172,7 +5661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L215"/>
+  <dimension ref="B1:L245"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="21.625" customWidth="1"/>
@@ -5748,7 +6237,7 @@
     </row>
     <row r="22" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="5">
-        <f t="shared" ref="C22:C40" si="0">C21+1</f>
+        <f t="shared" ref="C22:C45" si="0">C21+1</f>
         <v>1017</v>
       </c>
       <c r="D22" s="5">
@@ -5761,7 +6250,7 @@
         <v>631</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" ref="G22:G40" si="1">G21+1</f>
+        <f t="shared" ref="G22:G45" si="1">G21+1</f>
         <v>17</v>
       </c>
       <c r="H22" s="5">
@@ -6332,5353 +6821,6293 @@
         <v>120</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="41" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="41" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="5">
-        <v>2001</v>
+        <f t="shared" si="0"/>
+        <v>1036</v>
       </c>
       <c r="D41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>121</v>
+        <v>1033</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>599</v>
+        <v>1038</v>
       </c>
       <c r="G41" s="5">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="H41" s="5">
+        <v>7500000</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="42" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C42" s="5">
+        <f t="shared" si="0"/>
+        <v>1037</v>
+      </c>
+      <c r="D42" s="5">
         <v>1</v>
       </c>
-      <c r="H41" s="5">
-        <v>3000</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="42" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C42" s="5">
-        <v>2002</v>
-      </c>
-      <c r="D42" s="5">
-        <v>2</v>
-      </c>
       <c r="E42" s="5" t="s">
-        <v>124</v>
+        <v>1034</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>600</v>
+        <v>1039</v>
       </c>
       <c r="G42" s="5">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
       <c r="H42" s="5">
-        <v>6000</v>
+        <v>9000000</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>125</v>
+        <v>1044</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>126</v>
+        <v>1050</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="43" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="43" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="5">
-        <v>2003</v>
+        <f t="shared" si="0"/>
+        <v>1038</v>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>127</v>
+        <v>1035</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>648</v>
+        <v>1040</v>
       </c>
       <c r="G43" s="5">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
       <c r="H43" s="5">
-        <v>10000</v>
+        <v>10500000</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>128</v>
+        <v>1045</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>129</v>
+        <v>1052</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="44" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="44" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="5">
-        <v>2004</v>
+        <f t="shared" si="0"/>
+        <v>1039</v>
       </c>
       <c r="D44" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>130</v>
+        <v>1036</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>649</v>
+        <v>1041</v>
       </c>
       <c r="G44" s="5">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>39</v>
       </c>
       <c r="H44" s="5">
-        <v>15000</v>
+        <v>12000000</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>131</v>
+        <v>1046</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>132</v>
+        <v>1054</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="45" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="45" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="5">
-        <v>2005</v>
+        <f t="shared" si="0"/>
+        <v>1040</v>
       </c>
       <c r="D45" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>133</v>
+        <v>1037</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>601</v>
+        <v>1042</v>
       </c>
       <c r="G45" s="5">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="H45" s="5">
-        <v>22500</v>
+        <v>14000000</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>134</v>
+        <v>1047</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>135</v>
+        <v>1056</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>830</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="46" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="5">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="D46" s="5">
         <v>2</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>650</v>
+        <v>599</v>
       </c>
       <c r="G46" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H46" s="5">
-        <v>32500</v>
+        <v>3000</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>831</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="47" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="5">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="D47" s="5">
         <v>2</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="G47" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H47" s="5">
-        <v>45000</v>
+        <v>6000</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
     <row r="48" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="5">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="D48" s="5">
         <v>2</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="G48" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H48" s="5">
-        <v>60000</v>
+        <v>10000</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="5">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="D49" s="5">
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="G49" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H49" s="5">
-        <v>80000</v>
+        <v>15000</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
     </row>
     <row r="50" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="5">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>654</v>
+        <v>601</v>
       </c>
       <c r="G50" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H50" s="5">
-        <v>100000</v>
+        <v>22500</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
     </row>
     <row r="51" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="5">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D51" s="5">
         <v>2</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G51" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H51" s="5">
-        <v>120000</v>
+        <v>32500</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="52" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="52" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="5">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="D52" s="5">
         <v>2</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>602</v>
+        <v>651</v>
       </c>
       <c r="G52" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H52" s="5">
-        <v>140000</v>
+        <v>45000</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="53" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="5">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="D53" s="5">
         <v>2</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>603</v>
+        <v>652</v>
       </c>
       <c r="G53" s="5">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H53" s="5">
-        <v>160000</v>
+        <v>60000</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
     </row>
     <row r="54" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="5">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="D54" s="5">
         <v>2</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="G54" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H54" s="5">
-        <v>180000</v>
+        <v>80000</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="55" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="5">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="D55" s="5">
         <v>2</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>604</v>
+        <v>654</v>
       </c>
       <c r="G55" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H55" s="5">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="56" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="56" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="5">
-        <f>C55+1</f>
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="D56" s="5">
         <v>2</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>657</v>
+        <v>151</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="G56" s="5">
-        <f>G55+1</f>
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H56" s="5">
-        <v>230000</v>
+        <v>120000</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="57" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="5">
-        <f t="shared" ref="C57:C75" si="2">C56+1</f>
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="D57" s="5">
         <v>2</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>659</v>
+        <v>154</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>660</v>
+        <v>602</v>
       </c>
       <c r="G57" s="5">
-        <f t="shared" ref="G57:G75" si="3">G56+1</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H57" s="5">
-        <v>270000</v>
+        <v>140000</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="58" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="58" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="5">
-        <f t="shared" si="2"/>
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="D58" s="5">
         <v>2</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>661</v>
+        <v>157</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>662</v>
+        <v>603</v>
       </c>
       <c r="G58" s="5">
-        <f t="shared" si="3"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H58" s="5">
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="59" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="59" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="5">
-        <f t="shared" si="2"/>
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D59" s="5">
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>663</v>
+        <v>160</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="G59" s="5">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H59" s="5">
-        <v>380000</v>
+        <v>180000</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
     </row>
     <row r="60" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="5">
-        <f t="shared" si="2"/>
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D60" s="5">
         <v>2</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>665</v>
+        <v>163</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>666</v>
+        <v>604</v>
       </c>
       <c r="G60" s="5">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H60" s="5">
-        <v>450000</v>
+        <v>200000</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="61" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="5">
-        <f t="shared" si="2"/>
-        <v>2021</v>
+        <f>C60+1</f>
+        <v>2016</v>
       </c>
       <c r="D61" s="5">
         <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="G61" s="5">
-        <f t="shared" si="3"/>
-        <v>21</v>
+        <f>G60+1</f>
+        <v>16</v>
       </c>
       <c r="H61" s="5">
-        <v>520000</v>
+        <v>230000</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
     </row>
     <row r="62" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="5">
-        <f t="shared" si="2"/>
-        <v>2022</v>
+        <f t="shared" ref="C62:C85" si="2">C61+1</f>
+        <v>2017</v>
       </c>
       <c r="D62" s="5">
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="G62" s="5">
-        <f t="shared" si="3"/>
-        <v>22</v>
+        <f t="shared" ref="G62:G85" si="3">G61+1</f>
+        <v>17</v>
       </c>
       <c r="H62" s="5">
-        <v>600000</v>
+        <v>270000</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="63" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="5">
         <f t="shared" si="2"/>
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D63" s="5">
         <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="G63" s="5">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H63" s="5">
-        <v>680000</v>
+        <v>320000</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
     </row>
     <row r="64" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="5">
         <f t="shared" si="2"/>
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D64" s="5">
         <v>2</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="G64" s="5">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H64" s="5">
-        <v>760000</v>
+        <v>380000</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
     </row>
     <row r="65" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="5">
         <f t="shared" si="2"/>
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D65" s="5">
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="G65" s="5">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H65" s="5">
-        <v>850000</v>
+        <v>450000</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
     </row>
     <row r="66" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="5">
         <f t="shared" si="2"/>
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D66" s="5">
         <v>2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="G66" s="5">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H66" s="5">
-        <v>1000000</v>
+        <v>520000</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
     </row>
     <row r="67" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="5">
         <f t="shared" si="2"/>
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="D67" s="5">
         <v>2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G67" s="5">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H67" s="5">
-        <v>1250000</v>
+        <v>600000</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
     </row>
     <row r="68" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="5">
         <f t="shared" si="2"/>
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="D68" s="5">
         <v>2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H68" s="5">
-        <v>1500000</v>
+        <v>680000</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
     </row>
     <row r="69" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="5">
         <f t="shared" si="2"/>
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="D69" s="5">
         <v>2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H69" s="5">
-        <v>1750000</v>
+        <v>760000</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
     </row>
     <row r="70" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="5">
         <f t="shared" si="2"/>
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="D70" s="5">
         <v>2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H70" s="5">
-        <v>2000000</v>
+        <v>850000</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
     </row>
     <row r="71" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="5">
         <f t="shared" si="2"/>
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="D71" s="5">
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="3"/>
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H71" s="5">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
     </row>
     <row r="72" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="5">
         <f t="shared" si="2"/>
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="D72" s="5">
         <v>2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="3"/>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H72" s="5">
-        <v>3000000</v>
+        <v>1250000</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="73" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="5">
         <f t="shared" si="2"/>
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="D73" s="5">
         <v>2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H73" s="5">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
     </row>
     <row r="74" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="5">
         <f t="shared" si="2"/>
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="D74" s="5">
         <v>2</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="G74" s="5">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H74" s="5">
-        <v>5000000</v>
+        <v>1750000</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="75" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="5">
         <f t="shared" si="2"/>
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="D75" s="5">
         <v>2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="G75" s="5">
         <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H75" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="76" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C76" s="5">
+        <f t="shared" si="2"/>
+        <v>2031</v>
+      </c>
+      <c r="D76" s="5">
+        <v>2</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="G76" s="5">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H76" s="5">
+        <v>2500000</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="77" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C77" s="5">
+        <f t="shared" si="2"/>
+        <v>2032</v>
+      </c>
+      <c r="D77" s="5">
+        <v>2</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="G77" s="5">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H77" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="78" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C78" s="5">
+        <f t="shared" si="2"/>
+        <v>2033</v>
+      </c>
+      <c r="D78" s="5">
+        <v>2</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="G78" s="5">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H78" s="5">
+        <v>4000000</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="79" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C79" s="5">
+        <f t="shared" si="2"/>
+        <v>2034</v>
+      </c>
+      <c r="D79" s="5">
+        <v>2</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="G79" s="5">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H79" s="5">
+        <v>5000000</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="80" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C80" s="5">
+        <f t="shared" si="2"/>
+        <v>2035</v>
+      </c>
+      <c r="D80" s="5">
+        <v>2</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="G80" s="5">
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="H75" s="5">
+      <c r="H80" s="5">
         <v>6000000</v>
       </c>
-      <c r="I75" s="5" t="s">
+      <c r="I80" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="J80" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="K75" s="7" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="76" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C76" s="5">
-        <v>3001</v>
-      </c>
-      <c r="D76" s="5">
-        <v>3</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="G76" s="5">
-        <v>1</v>
-      </c>
-      <c r="H76" s="5">
-        <v>3000</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="J76" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="K76" s="7" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="77" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C77" s="5">
-        <v>3002</v>
-      </c>
-      <c r="D77" s="5">
-        <v>3</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="G77" s="5">
+      <c r="K80" s="7" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="81" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C81" s="5">
+        <f t="shared" si="2"/>
+        <v>2036</v>
+      </c>
+      <c r="D81" s="5">
         <v>2</v>
       </c>
-      <c r="H77" s="5">
-        <v>6000</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="K77" s="7" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="78" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C78" s="5">
-        <v>3003</v>
-      </c>
-      <c r="D78" s="5">
-        <v>3</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="G78" s="5">
-        <v>3</v>
-      </c>
-      <c r="H78" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I78" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="J78" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="K78" s="7" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="79" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C79" s="5">
-        <v>3004</v>
-      </c>
-      <c r="D79" s="5">
-        <v>3</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="G79" s="5">
-        <v>4</v>
-      </c>
-      <c r="H79" s="5">
-        <v>15000</v>
-      </c>
-      <c r="I79" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="80" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C80" s="5">
-        <v>3005</v>
-      </c>
-      <c r="D80" s="5">
-        <v>3</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="G80" s="5">
-        <v>5</v>
-      </c>
-      <c r="H80" s="5">
-        <v>22500</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="J80" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C81" s="5">
-        <v>3006</v>
-      </c>
-      <c r="D81" s="5">
-        <v>3</v>
-      </c>
       <c r="E81" s="5" t="s">
-        <v>221</v>
+        <v>1076</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>702</v>
+        <v>1081</v>
       </c>
       <c r="G81" s="5">
-        <v>6</v>
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="H81" s="5">
-        <v>32500</v>
+        <v>7500000</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>222</v>
+        <v>1060</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>223</v>
+        <v>1061</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="82" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C82" s="5">
-        <v>3007</v>
+        <f t="shared" si="2"/>
+        <v>2037</v>
       </c>
       <c r="D82" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>224</v>
+        <v>1077</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>703</v>
+        <v>1082</v>
       </c>
       <c r="G82" s="5">
-        <v>7</v>
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="H82" s="5">
-        <v>45000</v>
+        <v>9000000</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>225</v>
+        <v>1062</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>226</v>
+        <v>1063</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="83" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="83" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C83" s="5">
-        <v>3008</v>
+        <f t="shared" si="2"/>
+        <v>2038</v>
       </c>
       <c r="D83" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>227</v>
+        <v>1078</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>704</v>
+        <v>1083</v>
       </c>
       <c r="G83" s="5">
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="H83" s="5">
-        <v>60000</v>
+        <v>10500000</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>228</v>
+        <v>1064</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>229</v>
+        <v>1065</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="84" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="84" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C84" s="5">
-        <v>3009</v>
+        <f t="shared" si="2"/>
+        <v>2039</v>
       </c>
       <c r="D84" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>230</v>
+        <v>1079</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>705</v>
+        <v>1084</v>
       </c>
       <c r="G84" s="5">
-        <v>9</v>
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="H84" s="5">
-        <v>80000</v>
+        <v>12000000</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>231</v>
+        <v>1067</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>232</v>
+        <v>1068</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="85" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="85" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="5">
-        <v>3010</v>
+        <f t="shared" si="2"/>
+        <v>2040</v>
       </c>
       <c r="D85" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>233</v>
+        <v>1080</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>706</v>
+        <v>1085</v>
       </c>
       <c r="G85" s="5">
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="H85" s="5">
-        <v>100000</v>
+        <v>14000000</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>234</v>
+        <v>1069</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>235</v>
+        <v>1070</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>870</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="86" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="5">
-        <v>3011</v>
+        <v>3001</v>
       </c>
       <c r="D86" s="5">
         <v>3</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="G86" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H86" s="5">
-        <v>120000</v>
+        <v>3000</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="87" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="87" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="5">
-        <v>3012</v>
+        <v>3002</v>
       </c>
       <c r="D87" s="5">
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="G87" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H87" s="5">
-        <v>140000</v>
+        <v>6000</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
     </row>
     <row r="88" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" s="5">
-        <v>3013</v>
+        <v>3003</v>
       </c>
       <c r="D88" s="5">
         <v>3</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="G88" s="5">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H88" s="5">
-        <v>160000</v>
+        <v>10000</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
     </row>
     <row r="89" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C89" s="5">
-        <v>3014</v>
+        <v>3004</v>
       </c>
       <c r="D89" s="5">
         <v>3</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="G89" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H89" s="5">
-        <v>180000</v>
+        <v>15000</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="90" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C90" s="5">
-        <v>3015</v>
+        <v>3005</v>
       </c>
       <c r="D90" s="5">
         <v>3</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G90" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H90" s="5">
-        <v>200000</v>
+        <v>22500</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="91" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="91" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="5">
-        <f>C90+1</f>
-        <v>3016</v>
+        <v>3006</v>
       </c>
       <c r="D91" s="5">
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="G91" s="5">
-        <f>G90+1</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H91" s="5">
-        <v>230000</v>
+        <v>32500</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="92" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="92" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="5">
-        <f t="shared" ref="C92:C110" si="4">C91+1</f>
-        <v>3017</v>
+        <v>3007</v>
       </c>
       <c r="D92" s="5">
         <v>3</v>
       </c>
       <c r="E92" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="G92" s="5">
+        <v>7</v>
+      </c>
+      <c r="H92" s="5">
+        <v>45000</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K92" s="7" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="93" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C93" s="5">
+        <v>3008</v>
+      </c>
+      <c r="D93" s="5">
+        <v>3</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="G93" s="5">
+        <v>8</v>
+      </c>
+      <c r="H93" s="5">
+        <v>60000</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="94" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C94" s="5">
+        <v>3009</v>
+      </c>
+      <c r="D94" s="5">
+        <v>3</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="G94" s="5">
+        <v>9</v>
+      </c>
+      <c r="H94" s="5">
+        <v>80000</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="95" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C95" s="5">
+        <v>3010</v>
+      </c>
+      <c r="D95" s="5">
+        <v>3</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="G95" s="5">
+        <v>10</v>
+      </c>
+      <c r="H95" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="96" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C96" s="5">
+        <v>3011</v>
+      </c>
+      <c r="D96" s="5">
+        <v>3</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="G96" s="5">
+        <v>11</v>
+      </c>
+      <c r="H96" s="5">
+        <v>120000</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="97" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C97" s="5">
+        <v>3012</v>
+      </c>
+      <c r="D97" s="5">
+        <v>3</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="G97" s="5">
+        <v>12</v>
+      </c>
+      <c r="H97" s="5">
+        <v>140000</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="98" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C98" s="5">
+        <v>3013</v>
+      </c>
+      <c r="D98" s="5">
+        <v>3</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="G98" s="5">
+        <v>13</v>
+      </c>
+      <c r="H98" s="5">
+        <v>160000</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="99" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C99" s="5">
+        <v>3014</v>
+      </c>
+      <c r="D99" s="5">
+        <v>3</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="G99" s="5">
+        <v>14</v>
+      </c>
+      <c r="H99" s="5">
+        <v>180000</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="100" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C100" s="5">
+        <v>3015</v>
+      </c>
+      <c r="D100" s="5">
+        <v>3</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="G100" s="5">
+        <v>15</v>
+      </c>
+      <c r="H100" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="101" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C101" s="5">
+        <f>C100+1</f>
+        <v>3016</v>
+      </c>
+      <c r="D101" s="5">
+        <v>3</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="G101" s="5">
+        <f>G100+1</f>
+        <v>16</v>
+      </c>
+      <c r="H101" s="5">
+        <v>230000</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="102" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C102" s="5">
+        <f t="shared" ref="C102:C125" si="4">C101+1</f>
+        <v>3017</v>
+      </c>
+      <c r="D102" s="5">
+        <v>3</v>
+      </c>
+      <c r="E102" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="F102" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="G92" s="5">
-        <f t="shared" ref="G92:G110" si="5">G91+1</f>
+      <c r="G102" s="5">
+        <f t="shared" ref="G102:G125" si="5">G101+1</f>
         <v>17</v>
       </c>
-      <c r="H92" s="5">
+      <c r="H102" s="5">
         <v>270000</v>
       </c>
-      <c r="I92" s="5" t="s">
+      <c r="I102" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="J92" s="7" t="s">
+      <c r="J102" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="K92" s="7" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="93" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C93" s="5">
+      <c r="K102" s="7" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="103" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C103" s="5">
         <f t="shared" si="4"/>
         <v>3018</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D103" s="5">
         <v>3</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E103" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F103" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G103" s="5">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="H93" s="5">
+      <c r="H103" s="5">
         <v>320000</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="I103" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="J93" s="7" t="s">
+      <c r="J103" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="K93" s="7" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="94" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C94" s="5">
+      <c r="K103" s="7" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="104" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C104" s="5">
         <f t="shared" si="4"/>
         <v>3019</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D104" s="5">
         <v>3</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E104" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F104" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G104" s="5">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="H94" s="5">
+      <c r="H104" s="5">
         <v>380000</v>
       </c>
-      <c r="I94" s="5" t="s">
+      <c r="I104" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="J94" s="7" t="s">
+      <c r="J104" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="K94" s="7" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C95" s="5">
+      <c r="K104" s="7" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="105" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C105" s="5">
         <f t="shared" si="4"/>
         <v>3020</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D105" s="5">
         <v>3</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E105" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="F105" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="G95" s="5">
+      <c r="G105" s="5">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="H95" s="5">
+      <c r="H105" s="5">
         <v>450000</v>
       </c>
-      <c r="I95" s="5" t="s">
+      <c r="I105" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="J95" s="7" t="s">
+      <c r="J105" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="K95" s="7" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="96" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C96" s="5">
+      <c r="K105" s="7" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="106" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C106" s="5">
         <f t="shared" si="4"/>
         <v>3021</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D106" s="5">
         <v>3</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E106" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="F106" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="G96" s="5">
+      <c r="G106" s="5">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="H96" s="5">
+      <c r="H106" s="5">
         <v>520000</v>
       </c>
-      <c r="I96" s="5" t="s">
+      <c r="I106" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="J96" s="7" t="s">
+      <c r="J106" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="K96" s="7" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="97" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C97" s="5">
+      <c r="K106" s="7" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="107" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C107" s="5">
         <f t="shared" si="4"/>
         <v>3022</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D107" s="5">
         <v>3</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E107" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="F107" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="G97" s="5">
+      <c r="G107" s="5">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="H97" s="5">
+      <c r="H107" s="5">
         <v>600000</v>
       </c>
-      <c r="I97" s="5" t="s">
+      <c r="I107" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="J97" s="7" t="s">
+      <c r="J107" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="K97" s="7" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="98" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C98" s="5">
+      <c r="K107" s="7" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="108" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C108" s="5">
         <f t="shared" si="4"/>
         <v>3023</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D108" s="5">
         <v>3</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E108" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="F108" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="G98" s="5">
+      <c r="G108" s="5">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="H98" s="5">
+      <c r="H108" s="5">
         <v>680000</v>
       </c>
-      <c r="I98" s="5" t="s">
+      <c r="I108" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="J98" s="7" t="s">
+      <c r="J108" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="K98" s="7" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="99" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C99" s="5">
+      <c r="K108" s="7" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="109" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C109" s="5">
         <f t="shared" si="4"/>
         <v>3024</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D109" s="5">
         <v>3</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E109" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="F99" s="5" t="s">
+      <c r="F109" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="G99" s="5">
+      <c r="G109" s="5">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="H99" s="5">
+      <c r="H109" s="5">
         <v>760000</v>
       </c>
-      <c r="I99" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="J99" s="7" t="s">
+      <c r="J109" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="K99" s="7" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="100" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C100" s="5">
+      <c r="K109" s="7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="110" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C110" s="5">
         <f t="shared" si="4"/>
         <v>3025</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D110" s="5">
         <v>3</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E110" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="F110" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="G100" s="5">
+      <c r="G110" s="5">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
-      <c r="H100" s="5">
+      <c r="H110" s="5">
         <v>850000</v>
       </c>
-      <c r="I100" s="5" t="s">
+      <c r="I110" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="J100" s="7" t="s">
+      <c r="J110" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="K100" s="7" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C101" s="5">
+      <c r="K110" s="7" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="111" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C111" s="5">
         <f t="shared" si="4"/>
         <v>3026</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D111" s="5">
         <v>3</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E111" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F101" s="5" t="s">
+      <c r="F111" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="G101" s="5">
+      <c r="G111" s="5">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="H101" s="5">
+      <c r="H111" s="5">
         <v>1000000</v>
       </c>
-      <c r="I101" s="5" t="s">
+      <c r="I111" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="J101" s="7" t="s">
+      <c r="J111" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="K101" s="7" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C102" s="5">
+      <c r="K111" s="7" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="112" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C112" s="5">
         <f t="shared" si="4"/>
         <v>3027</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D112" s="5">
         <v>3</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E112" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="F102" s="5" t="s">
+      <c r="F112" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="G102" s="5">
+      <c r="G112" s="5">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
-      <c r="H102" s="5">
+      <c r="H112" s="5">
         <v>1250000</v>
       </c>
-      <c r="I102" s="5" t="s">
+      <c r="I112" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="J102" s="7" t="s">
+      <c r="J112" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="K102" s="7" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="103" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C103" s="5">
+      <c r="K112" s="7" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="113" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C113" s="5">
         <f t="shared" si="4"/>
         <v>3028</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D113" s="5">
         <v>3</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E113" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F103" s="5" t="s">
+      <c r="F113" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="G103" s="5">
+      <c r="G113" s="5">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
-      <c r="H103" s="5">
+      <c r="H113" s="5">
         <v>1500000</v>
       </c>
-      <c r="I103" s="5" t="s">
+      <c r="I113" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="J103" s="7" t="s">
+      <c r="J113" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="K103" s="7" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="104" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C104" s="5">
+      <c r="K113" s="7" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="114" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C114" s="5">
         <f t="shared" si="4"/>
         <v>3029</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D114" s="5">
         <v>3</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E114" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F114" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G114" s="5">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="H104" s="5">
+      <c r="H114" s="5">
         <v>1750000</v>
       </c>
-      <c r="I104" s="5" t="s">
+      <c r="I114" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="J104" s="7" t="s">
+      <c r="J114" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="K104" s="7" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="105" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C105" s="5">
+      <c r="K114" s="7" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="115" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C115" s="5">
         <f t="shared" si="4"/>
         <v>3030</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D115" s="5">
         <v>3</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E115" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="F105" s="5" t="s">
+      <c r="F115" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G115" s="5">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="H105" s="5">
+      <c r="H115" s="5">
         <v>2000000</v>
       </c>
-      <c r="I105" s="5" t="s">
+      <c r="I115" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="J105" s="7" t="s">
+      <c r="J115" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="K105" s="7" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="106" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C106" s="5">
+      <c r="K115" s="7" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="116" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C116" s="5">
         <f t="shared" si="4"/>
         <v>3031</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D116" s="5">
         <v>3</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E116" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F106" s="5" t="s">
+      <c r="F116" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="G106" s="5">
+      <c r="G116" s="5">
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="H106" s="5">
+      <c r="H116" s="5">
         <v>2500000</v>
       </c>
-      <c r="I106" s="5" t="s">
+      <c r="I116" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="J106" s="7" t="s">
+      <c r="J116" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="K106" s="7" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="107" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C107" s="5">
+      <c r="K116" s="7" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="117" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C117" s="5">
         <f t="shared" si="4"/>
         <v>3032</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D117" s="5">
         <v>3</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E117" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="F117" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="G107" s="5">
+      <c r="G117" s="5">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="H107" s="5">
+      <c r="H117" s="5">
         <v>3000000</v>
       </c>
-      <c r="I107" s="5" t="s">
+      <c r="I117" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="J107" s="7" t="s">
+      <c r="J117" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="K107" s="7" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="108" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C108" s="5">
+      <c r="K117" s="7" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="118" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C118" s="5">
         <f t="shared" si="4"/>
         <v>3033</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D118" s="5">
         <v>3</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E118" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="F118" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="G108" s="5">
+      <c r="G118" s="5">
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="H108" s="5">
+      <c r="H118" s="5">
         <v>4000000</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="I118" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="J108" s="7" t="s">
+      <c r="J118" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="K108" s="7" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="109" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C109" s="5">
+      <c r="K118" s="7" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="119" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C119" s="5">
         <f t="shared" si="4"/>
         <v>3034</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D119" s="5">
         <v>3</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E119" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="F119" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G119" s="5">
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="H109" s="5">
+      <c r="H119" s="5">
         <v>5000000</v>
       </c>
-      <c r="I109" s="5" t="s">
+      <c r="I119" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="J109" s="7" t="s">
+      <c r="J119" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="K109" s="7" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="110" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C110" s="5">
+      <c r="K119" s="7" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="120" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C120" s="5">
         <f t="shared" si="4"/>
         <v>3035</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D120" s="5">
         <v>3</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E120" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="F110" s="5" t="s">
+      <c r="F120" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G120" s="5">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="H110" s="5">
+      <c r="H120" s="5">
         <v>6000000</v>
       </c>
-      <c r="I110" s="5" t="s">
+      <c r="I120" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="J110" s="7" t="s">
+      <c r="J120" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="K110" s="7" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="111" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C111" s="5">
-        <v>4001</v>
-      </c>
-      <c r="D111" s="5">
-        <v>4</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="G111" s="5">
-        <v>1</v>
-      </c>
-      <c r="H111" s="5">
-        <v>3000</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="J111" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="K111" s="7" t="s">
-        <v>896</v>
-      </c>
-      <c r="L111" s="8"/>
-    </row>
-    <row r="112" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C112" s="5">
-        <v>4002</v>
-      </c>
-      <c r="D112" s="5">
-        <v>4</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="G112" s="5">
-        <v>2</v>
-      </c>
-      <c r="H112" s="5">
-        <v>6000</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="J112" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="K112" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="L112" s="8"/>
-    </row>
-    <row r="113" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C113" s="5">
-        <v>4003</v>
-      </c>
-      <c r="D113" s="5">
-        <v>4</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>733</v>
-      </c>
-      <c r="G113" s="5">
+      <c r="K120" s="7" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="121" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C121" s="5">
+        <f t="shared" si="4"/>
+        <v>3036</v>
+      </c>
+      <c r="D121" s="5">
         <v>3</v>
       </c>
-      <c r="H113" s="5">
-        <v>10000</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="J113" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="K113" s="7" t="s">
-        <v>898</v>
-      </c>
-      <c r="L113" s="8"/>
-    </row>
-    <row r="114" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C114" s="5">
-        <v>4004</v>
-      </c>
-      <c r="D114" s="5">
-        <v>4</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>734</v>
-      </c>
-      <c r="G114" s="5">
-        <v>4</v>
-      </c>
-      <c r="H114" s="5">
-        <v>15000</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="J114" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="K114" s="7" t="s">
-        <v>899</v>
-      </c>
-      <c r="L114" s="8"/>
-    </row>
-    <row r="115" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C115" s="5">
-        <v>4005</v>
-      </c>
-      <c r="D115" s="5">
-        <v>4</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="G115" s="5">
-        <v>5</v>
-      </c>
-      <c r="H115" s="5">
-        <v>22500</v>
-      </c>
-      <c r="I115" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="K115" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="L115" s="8"/>
-    </row>
-    <row r="116" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C116" s="5">
-        <v>4006</v>
-      </c>
-      <c r="D116" s="5">
-        <v>4</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="G116" s="5">
-        <v>6</v>
-      </c>
-      <c r="H116" s="5">
-        <v>32500</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="J116" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="K116" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="L116" s="8"/>
-    </row>
-    <row r="117" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C117" s="5">
-        <v>4007</v>
-      </c>
-      <c r="D117" s="5">
-        <v>4</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G117" s="5">
-        <v>7</v>
-      </c>
-      <c r="H117" s="5">
-        <v>45000</v>
-      </c>
-      <c r="I117" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="J117" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="K117" s="7" t="s">
-        <v>902</v>
-      </c>
-      <c r="L117" s="8"/>
-    </row>
-    <row r="118" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C118" s="5">
-        <v>4008</v>
-      </c>
-      <c r="D118" s="5">
-        <v>4</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G118" s="5">
-        <v>8</v>
-      </c>
-      <c r="H118" s="5">
-        <v>60000</v>
-      </c>
-      <c r="I118" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="J118" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="K118" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="L118" s="8"/>
-    </row>
-    <row r="119" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C119" s="5">
-        <v>4009</v>
-      </c>
-      <c r="D119" s="5">
-        <v>4</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="G119" s="5">
-        <v>9</v>
-      </c>
-      <c r="H119" s="5">
-        <v>80000</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="J119" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="K119" s="7" t="s">
-        <v>904</v>
-      </c>
-      <c r="L119" s="8"/>
-    </row>
-    <row r="120" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C120" s="5">
-        <v>4010</v>
-      </c>
-      <c r="D120" s="5">
-        <v>4</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="G120" s="5">
-        <v>10</v>
-      </c>
-      <c r="H120" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I120" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="J120" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="K120" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="L120" s="8"/>
-    </row>
-    <row r="121" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C121" s="5">
-        <v>4011</v>
-      </c>
-      <c r="D121" s="5">
-        <v>4</v>
-      </c>
       <c r="E121" s="5" t="s">
-        <v>341</v>
+        <v>1086</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>737</v>
+        <v>1087</v>
       </c>
       <c r="G121" s="5">
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>36</v>
       </c>
       <c r="H121" s="5">
-        <v>120000</v>
+        <v>7500000</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>342</v>
+        <v>1099</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>343</v>
+        <v>1096</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="L121" s="8"/>
+        <v>1106</v>
+      </c>
     </row>
     <row r="122" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C122" s="5">
-        <v>4012</v>
+        <f t="shared" si="4"/>
+        <v>3037</v>
       </c>
       <c r="D122" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>344</v>
+        <v>1088</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>610</v>
+        <v>1089</v>
       </c>
       <c r="G122" s="5">
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
       <c r="H122" s="5">
-        <v>140000</v>
+        <v>9000000</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>345</v>
+        <v>1100</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>346</v>
+        <v>1105</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="L122" s="8"/>
-    </row>
-    <row r="123" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="123" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C123" s="5">
-        <v>4013</v>
+        <f t="shared" si="4"/>
+        <v>3038</v>
       </c>
       <c r="D123" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>347</v>
+        <v>1090</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>738</v>
+        <v>1091</v>
       </c>
       <c r="G123" s="5">
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>38</v>
       </c>
       <c r="H123" s="5">
-        <v>160000</v>
+        <v>10500000</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>348</v>
+        <v>1101</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>349</v>
+        <v>1097</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="L123" s="8"/>
-    </row>
-    <row r="124" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="124" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C124" s="5">
-        <v>4014</v>
+        <f t="shared" si="4"/>
+        <v>3039</v>
       </c>
       <c r="D124" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>350</v>
+        <v>1092</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>611</v>
+        <v>1093</v>
       </c>
       <c r="G124" s="5">
-        <v>14</v>
+        <f t="shared" si="5"/>
+        <v>39</v>
       </c>
       <c r="H124" s="5">
-        <v>180000</v>
+        <v>12000000</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>351</v>
+        <v>1102</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>352</v>
+        <v>1104</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="L124" s="8"/>
+        <v>1109</v>
+      </c>
     </row>
     <row r="125" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C125" s="5">
-        <v>4015</v>
+        <f t="shared" si="4"/>
+        <v>3040</v>
       </c>
       <c r="D125" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>353</v>
+        <v>1094</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>739</v>
+        <v>1095</v>
       </c>
       <c r="G125" s="5">
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="H125" s="5">
-        <v>200000</v>
+        <v>14000000</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>354</v>
+        <v>1103</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>355</v>
+        <v>1098</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="L125" s="8"/>
-    </row>
-    <row r="126" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="126" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C126" s="5">
-        <f>C125+1</f>
-        <v>4016</v>
+        <v>4001</v>
       </c>
       <c r="D126" s="5">
         <v>4</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>356</v>
+        <v>311</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>740</v>
+        <v>605</v>
       </c>
       <c r="G126" s="5">
-        <f>G125+1</f>
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H126" s="5">
-        <v>230000</v>
+        <v>3000</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="L126" s="8"/>
     </row>
-    <row r="127" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C127" s="5">
-        <f t="shared" ref="C127:C145" si="6">C126+1</f>
-        <v>4017</v>
+        <v>4002</v>
       </c>
       <c r="D127" s="5">
         <v>4</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>612</v>
+        <v>732</v>
       </c>
       <c r="G127" s="5">
-        <f t="shared" ref="G127:G145" si="7">G126+1</f>
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H127" s="5">
-        <v>270000</v>
+        <v>6000</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="L127" s="8"/>
     </row>
-    <row r="128" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C128" s="5">
-        <f t="shared" si="6"/>
-        <v>4018</v>
+        <v>4003</v>
       </c>
       <c r="D128" s="5">
         <v>4</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="G128" s="5">
-        <f t="shared" si="7"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H128" s="5">
-        <v>320000</v>
+        <v>10000</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>364</v>
+        <v>319</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="L128" s="8"/>
     </row>
-    <row r="129" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C129" s="5">
-        <f t="shared" si="6"/>
-        <v>4019</v>
+        <v>4004</v>
       </c>
       <c r="D129" s="5">
         <v>4</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="G129" s="5">
-        <f t="shared" si="7"/>
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H129" s="5">
-        <v>380000</v>
+        <v>15000</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>367</v>
+        <v>322</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="L129" s="8"/>
     </row>
-    <row r="130" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C130" s="5">
-        <f t="shared" si="6"/>
-        <v>4020</v>
+        <v>4005</v>
       </c>
       <c r="D130" s="5">
         <v>4</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>613</v>
+        <v>735</v>
       </c>
       <c r="G130" s="5">
-        <f t="shared" si="7"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H130" s="5">
-        <v>450000</v>
+        <v>22500</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>369</v>
+        <v>324</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="L130" s="8"/>
     </row>
-    <row r="131" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C131" s="5">
-        <f t="shared" si="6"/>
-        <v>4021</v>
+        <v>4006</v>
       </c>
       <c r="D131" s="5">
         <v>4</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>614</v>
+        <v>736</v>
       </c>
       <c r="G131" s="5">
-        <f t="shared" si="7"/>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H131" s="5">
-        <v>520000</v>
+        <v>32500</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="L131" s="8"/>
     </row>
-    <row r="132" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C132" s="5">
-        <f t="shared" si="6"/>
-        <v>4022</v>
+        <v>4007</v>
       </c>
       <c r="D132" s="5">
         <v>4</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>374</v>
+        <v>329</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>743</v>
+        <v>606</v>
       </c>
       <c r="G132" s="5">
-        <f t="shared" si="7"/>
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H132" s="5">
-        <v>600000</v>
+        <v>45000</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="L132" s="8"/>
     </row>
-    <row r="133" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C133" s="5">
-        <f t="shared" si="6"/>
-        <v>4023</v>
+        <v>4008</v>
       </c>
       <c r="D133" s="5">
         <v>4</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>377</v>
+        <v>332</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>744</v>
+        <v>607</v>
       </c>
       <c r="G133" s="5">
-        <f t="shared" si="7"/>
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H133" s="5">
-        <v>680000</v>
+        <v>60000</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="L133" s="8"/>
     </row>
-    <row r="134" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C134" s="5">
-        <f t="shared" si="6"/>
-        <v>4024</v>
+        <v>4009</v>
       </c>
       <c r="D134" s="5">
         <v>4</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>745</v>
+        <v>608</v>
       </c>
       <c r="G134" s="5">
-        <f t="shared" si="7"/>
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H134" s="5">
-        <v>760000</v>
+        <v>80000</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>381</v>
+        <v>336</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>382</v>
+        <v>337</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="L134" s="8"/>
     </row>
-    <row r="135" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C135" s="5">
-        <f t="shared" si="6"/>
-        <v>4025</v>
+        <v>4010</v>
       </c>
       <c r="D135" s="5">
         <v>4</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>746</v>
+        <v>609</v>
       </c>
       <c r="G135" s="5">
-        <f t="shared" si="7"/>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H135" s="5">
-        <v>850000</v>
+        <v>100000</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
       <c r="L135" s="8"/>
     </row>
-    <row r="136" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C136" s="5">
-        <f t="shared" si="6"/>
-        <v>4026</v>
+        <v>4011</v>
       </c>
       <c r="D136" s="5">
         <v>4</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="G136" s="5">
-        <f t="shared" si="7"/>
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H136" s="5">
-        <v>1000000</v>
+        <v>120000</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="L136" s="8"/>
     </row>
     <row r="137" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C137" s="5">
-        <f t="shared" si="6"/>
-        <v>4027</v>
+        <v>4012</v>
       </c>
       <c r="D137" s="5">
         <v>4</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="G137" s="5">
-        <f t="shared" si="7"/>
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H137" s="5">
-        <v>1250000</v>
+        <v>140000</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C138" s="5">
-        <f t="shared" si="6"/>
-        <v>4028</v>
+        <v>4013</v>
       </c>
       <c r="D138" s="5">
         <v>4</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="G138" s="5">
-        <f t="shared" si="7"/>
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H138" s="5">
-        <v>1500000</v>
+        <v>160000</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>394</v>
+        <v>349</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="L138" s="8"/>
     </row>
-    <row r="139" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C139" s="5">
-        <f t="shared" si="6"/>
-        <v>4029</v>
+        <v>4014</v>
       </c>
       <c r="D139" s="5">
         <v>4</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>749</v>
+        <v>611</v>
       </c>
       <c r="G139" s="5">
-        <f t="shared" si="7"/>
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H139" s="5">
-        <v>1750000</v>
+        <v>180000</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="L139" s="8"/>
     </row>
     <row r="140" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C140" s="5">
-        <f t="shared" si="6"/>
-        <v>4030</v>
+        <v>4015</v>
       </c>
       <c r="D140" s="5">
         <v>4</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>616</v>
+        <v>739</v>
       </c>
       <c r="G140" s="5">
-        <f t="shared" si="7"/>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H140" s="5">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="L140" s="8"/>
     </row>
     <row r="141" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C141" s="5">
-        <f t="shared" si="6"/>
-        <v>4031</v>
+        <f>C140+1</f>
+        <v>4016</v>
       </c>
       <c r="D141" s="5">
         <v>4</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="G141" s="5">
-        <f t="shared" si="7"/>
-        <v>31</v>
+        <f>G140+1</f>
+        <v>16</v>
       </c>
       <c r="H141" s="5">
-        <v>2500000</v>
+        <v>230000</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>402</v>
+        <v>357</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="L141" s="8"/>
     </row>
     <row r="142" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C142" s="5">
-        <f t="shared" si="6"/>
-        <v>4032</v>
+        <f t="shared" ref="C142:C165" si="6">C141+1</f>
+        <v>4017</v>
       </c>
       <c r="D142" s="5">
         <v>4</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>404</v>
+        <v>359</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="G142" s="5">
-        <f t="shared" si="7"/>
-        <v>32</v>
+        <f t="shared" ref="G142:G165" si="7">G141+1</f>
+        <v>17</v>
       </c>
       <c r="H142" s="5">
-        <v>3000000</v>
+        <v>270000</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="L142" s="8"/>
     </row>
     <row r="143" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C143" s="5">
         <f t="shared" si="6"/>
-        <v>4033</v>
+        <v>4018</v>
       </c>
       <c r="D143" s="5">
         <v>4</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>407</v>
+        <v>362</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="G143" s="5">
         <f t="shared" si="7"/>
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H143" s="5">
-        <v>4000000</v>
+        <v>320000</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="L143" s="8"/>
     </row>
     <row r="144" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C144" s="5">
         <f t="shared" si="6"/>
-        <v>4034</v>
+        <v>4019</v>
       </c>
       <c r="D144" s="5">
         <v>4</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="G144" s="5">
         <f t="shared" si="7"/>
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H144" s="5">
-        <v>5000000</v>
+        <v>380000</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>411</v>
+        <v>366</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>412</v>
+        <v>367</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="L144" s="8"/>
     </row>
     <row r="145" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C145" s="5">
         <f t="shared" si="6"/>
-        <v>4035</v>
+        <v>4020</v>
       </c>
       <c r="D145" s="5">
         <v>4</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>413</v>
+        <v>368</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>753</v>
+        <v>613</v>
       </c>
       <c r="G145" s="5">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H145" s="5">
-        <v>6000000</v>
+        <v>450000</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="L145" s="8"/>
     </row>
-    <row r="146" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C146" s="5">
-        <v>5001</v>
+        <f t="shared" si="6"/>
+        <v>4021</v>
       </c>
       <c r="D146" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>754</v>
+        <v>614</v>
       </c>
       <c r="G146" s="5">
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>21</v>
       </c>
       <c r="H146" s="5">
-        <v>3000</v>
+        <v>520000</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="K146" s="7" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="147" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>913</v>
+      </c>
+      <c r="L146" s="8"/>
+    </row>
+    <row r="147" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C147" s="5">
-        <v>5002</v>
+        <f t="shared" si="6"/>
+        <v>4022</v>
       </c>
       <c r="D147" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="G147" s="5">
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="H147" s="5">
-        <v>6000</v>
+        <v>600000</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>421</v>
+        <v>376</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="148" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>914</v>
+      </c>
+      <c r="L147" s="8"/>
+    </row>
+    <row r="148" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C148" s="5">
-        <v>5003</v>
+        <f t="shared" si="6"/>
+        <v>4023</v>
       </c>
       <c r="D148" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>422</v>
+        <v>377</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="G148" s="5">
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>23</v>
       </c>
       <c r="H148" s="5">
-        <v>10000</v>
+        <v>680000</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>424</v>
+        <v>379</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="149" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>915</v>
+      </c>
+      <c r="L148" s="8"/>
+    </row>
+    <row r="149" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C149" s="5">
-        <v>5004</v>
+        <f t="shared" si="6"/>
+        <v>4024</v>
       </c>
       <c r="D149" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>425</v>
+        <v>380</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="G149" s="5">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="H149" s="5">
+        <v>760000</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J149" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="L149" s="8"/>
+    </row>
+    <row r="150" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C150" s="5">
+        <f t="shared" si="6"/>
+        <v>4025</v>
+      </c>
+      <c r="D150" s="5">
         <v>4</v>
       </c>
-      <c r="H149" s="5">
-        <v>15000</v>
-      </c>
-      <c r="I149" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="J149" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="150" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C150" s="5">
-        <v>5005</v>
-      </c>
-      <c r="D150" s="5">
-        <v>5</v>
-      </c>
       <c r="E150" s="5" t="s">
-        <v>428</v>
+        <v>383</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="G150" s="5">
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="H150" s="5">
-        <v>22500</v>
+        <v>850000</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="K150" s="7" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="151" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>917</v>
+      </c>
+      <c r="L150" s="8"/>
+    </row>
+    <row r="151" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C151" s="5">
-        <v>5006</v>
+        <f t="shared" si="6"/>
+        <v>4026</v>
       </c>
       <c r="D151" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>431</v>
+        <v>386</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="G151" s="5">
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="H151" s="5">
-        <v>32500</v>
+        <v>1000000</v>
       </c>
       <c r="I151" s="5" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>433</v>
+        <v>388</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="152" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>918</v>
+      </c>
+      <c r="L151" s="8"/>
+    </row>
+    <row r="152" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C152" s="5">
-        <v>5007</v>
+        <f t="shared" si="6"/>
+        <v>4027</v>
       </c>
       <c r="D152" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>760</v>
+        <v>615</v>
       </c>
       <c r="G152" s="5">
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="H152" s="5">
-        <v>45000</v>
+        <v>1250000</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="K152" s="7" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="153" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>919</v>
+      </c>
+      <c r="L152" s="8"/>
+    </row>
+    <row r="153" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C153" s="5">
-        <v>5008</v>
+        <f t="shared" si="6"/>
+        <v>4028</v>
       </c>
       <c r="D153" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="G153" s="5">
-        <v>8</v>
+        <f t="shared" si="7"/>
+        <v>28</v>
       </c>
       <c r="H153" s="5">
-        <v>60000</v>
+        <v>1500000</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>438</v>
+        <v>393</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="K153" s="7" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="154" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>920</v>
+      </c>
+      <c r="L153" s="8"/>
+    </row>
+    <row r="154" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C154" s="5">
-        <v>5009</v>
+        <f t="shared" si="6"/>
+        <v>4029</v>
       </c>
       <c r="D154" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="G154" s="5">
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="H154" s="5">
-        <v>80000</v>
+        <v>1750000</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="155" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>921</v>
+      </c>
+      <c r="L154" s="8"/>
+    </row>
+    <row r="155" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C155" s="5">
-        <v>5010</v>
+        <f t="shared" si="6"/>
+        <v>4030</v>
       </c>
       <c r="D155" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>763</v>
+        <v>616</v>
       </c>
       <c r="G155" s="5">
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>30</v>
       </c>
       <c r="H155" s="5">
-        <v>100000</v>
+        <v>2000000</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="156" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>922</v>
+      </c>
+      <c r="L155" s="8"/>
+    </row>
+    <row r="156" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C156" s="5">
-        <v>5011</v>
+        <f t="shared" si="6"/>
+        <v>4031</v>
       </c>
       <c r="D156" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="G156" s="5">
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>31</v>
       </c>
       <c r="H156" s="5">
-        <v>120000</v>
+        <v>2500000</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>941</v>
-      </c>
+        <v>923</v>
+      </c>
+      <c r="L156" s="8"/>
     </row>
     <row r="157" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C157" s="5">
-        <v>5012</v>
+        <f t="shared" si="6"/>
+        <v>4032</v>
       </c>
       <c r="D157" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>449</v>
+        <v>404</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>765</v>
+        <v>617</v>
       </c>
       <c r="G157" s="5">
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="H157" s="5">
-        <v>140000</v>
+        <v>3000000</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="158" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>924</v>
+      </c>
+      <c r="L157" s="8"/>
+    </row>
+    <row r="158" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C158" s="5">
-        <v>5013</v>
+        <f t="shared" si="6"/>
+        <v>4033</v>
       </c>
       <c r="D158" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="G158" s="5">
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="H158" s="5">
-        <v>160000</v>
+        <v>4000000</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="159" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>925</v>
+      </c>
+      <c r="L158" s="8"/>
+    </row>
+    <row r="159" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C159" s="5">
-        <v>5014</v>
+        <f t="shared" si="6"/>
+        <v>4034</v>
       </c>
       <c r="D159" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="G159" s="5">
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="H159" s="5">
-        <v>180000</v>
+        <v>5000000</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>944</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="L159" s="8"/>
     </row>
     <row r="160" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C160" s="5">
+        <f t="shared" si="6"/>
+        <v>4035</v>
+      </c>
+      <c r="D160" s="5">
+        <v>4</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="G160" s="5">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="H160" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="L160" s="8"/>
+    </row>
+    <row r="161" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C161" s="5">
+        <f t="shared" si="6"/>
+        <v>4036</v>
+      </c>
+      <c r="D161" s="5">
+        <v>4</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G161" s="5">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="H161" s="5">
+        <v>7500000</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="L161" s="8"/>
+    </row>
+    <row r="162" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C162" s="5">
+        <f t="shared" si="6"/>
+        <v>4037</v>
+      </c>
+      <c r="D162" s="5">
+        <v>4</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G162" s="5">
+        <f t="shared" si="7"/>
+        <v>37</v>
+      </c>
+      <c r="H162" s="5">
+        <v>9000000</v>
+      </c>
+      <c r="I162" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="L162" s="8"/>
+    </row>
+    <row r="163" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C163" s="5">
+        <f t="shared" si="6"/>
+        <v>4038</v>
+      </c>
+      <c r="D163" s="5">
+        <v>4</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G163" s="5">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="H163" s="5">
+        <v>10500000</v>
+      </c>
+      <c r="I163" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="L163" s="8"/>
+    </row>
+    <row r="164" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C164" s="5">
+        <f t="shared" si="6"/>
+        <v>4039</v>
+      </c>
+      <c r="D164" s="5">
+        <v>4</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G164" s="5">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="H164" s="5">
+        <v>12000000</v>
+      </c>
+      <c r="I164" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L164" s="8"/>
+    </row>
+    <row r="165" spans="3:12" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C165" s="5">
+        <f t="shared" si="6"/>
+        <v>4040</v>
+      </c>
+      <c r="D165" s="5">
+        <v>4</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G165" s="5">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H165" s="5">
+        <v>14000000</v>
+      </c>
+      <c r="I165" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="J165" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L165" s="8"/>
+    </row>
+    <row r="166" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C166" s="5">
+        <v>5001</v>
+      </c>
+      <c r="D166" s="5">
+        <v>5</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="G166" s="5">
+        <v>1</v>
+      </c>
+      <c r="H166" s="5">
+        <v>3000</v>
+      </c>
+      <c r="I166" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="J166" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="167" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C167" s="5">
+        <v>5002</v>
+      </c>
+      <c r="D167" s="5">
+        <v>5</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="G167" s="5">
+        <v>2</v>
+      </c>
+      <c r="H167" s="5">
+        <v>6000</v>
+      </c>
+      <c r="I167" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="J167" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="K167" s="7" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="168" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C168" s="5">
+        <v>5003</v>
+      </c>
+      <c r="D168" s="5">
+        <v>5</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="G168" s="5">
+        <v>3</v>
+      </c>
+      <c r="H168" s="5">
+        <v>10000</v>
+      </c>
+      <c r="I168" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="J168" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="169" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C169" s="5">
+        <v>5004</v>
+      </c>
+      <c r="D169" s="5">
+        <v>5</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G169" s="5">
+        <v>4</v>
+      </c>
+      <c r="H169" s="5">
+        <v>15000</v>
+      </c>
+      <c r="I169" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="J169" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="170" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C170" s="5">
+        <v>5005</v>
+      </c>
+      <c r="D170" s="5">
+        <v>5</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="G170" s="5">
+        <v>5</v>
+      </c>
+      <c r="H170" s="5">
+        <v>22500</v>
+      </c>
+      <c r="I170" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="171" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C171" s="5">
+        <v>5006</v>
+      </c>
+      <c r="D171" s="5">
+        <v>5</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="G171" s="5">
+        <v>6</v>
+      </c>
+      <c r="H171" s="5">
+        <v>32500</v>
+      </c>
+      <c r="I171" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="J171" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="K171" s="7" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="172" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C172" s="5">
+        <v>5007</v>
+      </c>
+      <c r="D172" s="5">
+        <v>5</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="G172" s="5">
+        <v>7</v>
+      </c>
+      <c r="H172" s="5">
+        <v>45000</v>
+      </c>
+      <c r="I172" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="J172" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="173" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C173" s="5">
+        <v>5008</v>
+      </c>
+      <c r="D173" s="5">
+        <v>5</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="G173" s="5">
+        <v>8</v>
+      </c>
+      <c r="H173" s="5">
+        <v>60000</v>
+      </c>
+      <c r="I173" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="J173" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="174" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C174" s="5">
+        <v>5009</v>
+      </c>
+      <c r="D174" s="5">
+        <v>5</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="G174" s="5">
+        <v>9</v>
+      </c>
+      <c r="H174" s="5">
+        <v>80000</v>
+      </c>
+      <c r="I174" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="J174" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="175" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C175" s="5">
+        <v>5010</v>
+      </c>
+      <c r="D175" s="5">
+        <v>5</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="G175" s="5">
+        <v>10</v>
+      </c>
+      <c r="H175" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I175" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="J175" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="K175" s="7" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="176" spans="3:12" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C176" s="5">
+        <v>5011</v>
+      </c>
+      <c r="D176" s="5">
+        <v>5</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="G176" s="5">
+        <v>11</v>
+      </c>
+      <c r="H176" s="5">
+        <v>120000</v>
+      </c>
+      <c r="I176" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J176" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="K176" s="7" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="177" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C177" s="5">
+        <v>5012</v>
+      </c>
+      <c r="D177" s="5">
+        <v>5</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="G177" s="5">
+        <v>12</v>
+      </c>
+      <c r="H177" s="5">
+        <v>140000</v>
+      </c>
+      <c r="I177" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="J177" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="178" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C178" s="5">
+        <v>5013</v>
+      </c>
+      <c r="D178" s="5">
+        <v>5</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="G178" s="5">
+        <v>13</v>
+      </c>
+      <c r="H178" s="5">
+        <v>160000</v>
+      </c>
+      <c r="I178" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="179" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C179" s="5">
+        <v>5014</v>
+      </c>
+      <c r="D179" s="5">
+        <v>5</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="G179" s="5">
+        <v>14</v>
+      </c>
+      <c r="H179" s="5">
+        <v>180000</v>
+      </c>
+      <c r="I179" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="180" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C180" s="5">
         <v>5015</v>
       </c>
-      <c r="D160" s="5">
+      <c r="D180" s="5">
         <v>5</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E180" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="F160" s="5" t="s">
+      <c r="F180" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="G160" s="5">
+      <c r="G180" s="5">
         <v>15</v>
       </c>
-      <c r="H160" s="5">
+      <c r="H180" s="5">
         <v>200000</v>
       </c>
-      <c r="I160" s="5" t="s">
+      <c r="I180" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="J160" s="7" t="s">
+      <c r="J180" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="K160" s="7" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="161" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C161" s="5">
-        <f>C160+1</f>
+      <c r="K180" s="7" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="181" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C181" s="5">
+        <f>C180+1</f>
         <v>5016</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D181" s="5">
         <v>5</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E181" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="F161" s="5" t="s">
+      <c r="F181" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="G161" s="5">
-        <f>G160+1</f>
+      <c r="G181" s="5">
+        <f>G180+1</f>
         <v>16</v>
       </c>
-      <c r="H161" s="5">
+      <c r="H181" s="5">
         <v>230000</v>
       </c>
-      <c r="I161" s="5" t="s">
+      <c r="I181" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="J161" s="7" t="s">
+      <c r="J181" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="K161" s="7" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="162" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C162" s="5">
-        <f t="shared" ref="C162:C180" si="8">C161+1</f>
+      <c r="K181" s="7" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="182" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C182" s="5">
+        <f t="shared" ref="C182:C205" si="8">C181+1</f>
         <v>5017</v>
       </c>
-      <c r="D162" s="5">
+      <c r="D182" s="5">
         <v>5</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="E182" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F182" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="G162" s="5">
-        <f t="shared" ref="G162:G180" si="9">G161+1</f>
+      <c r="G182" s="5">
+        <f t="shared" ref="G182:G205" si="9">G181+1</f>
         <v>17</v>
       </c>
-      <c r="H162" s="5">
+      <c r="H182" s="5">
         <v>270000</v>
       </c>
-      <c r="I162" s="5" t="s">
+      <c r="I182" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="J162" s="7" t="s">
+      <c r="J182" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="K162" s="7" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="163" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C163" s="5">
+      <c r="K182" s="7" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="183" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C183" s="5">
         <f t="shared" si="8"/>
         <v>5018</v>
       </c>
-      <c r="D163" s="5">
+      <c r="D183" s="5">
         <v>5</v>
       </c>
-      <c r="E163" s="5" t="s">
+      <c r="E183" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F183" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="G163" s="5">
+      <c r="G183" s="5">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="H163" s="5">
+      <c r="H183" s="5">
         <v>320000</v>
       </c>
-      <c r="I163" s="5" t="s">
+      <c r="I183" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="J163" s="7" t="s">
+      <c r="J183" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="K163" s="7" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="164" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C164" s="5">
+      <c r="K183" s="7" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="184" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C184" s="5">
         <f t="shared" si="8"/>
         <v>5019</v>
       </c>
-      <c r="D164" s="5">
+      <c r="D184" s="5">
         <v>5</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="E184" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="F184" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="G164" s="5">
+      <c r="G184" s="5">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="H164" s="5">
+      <c r="H184" s="5">
         <v>380000</v>
       </c>
-      <c r="I164" s="5" t="s">
+      <c r="I184" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="J164" s="7" t="s">
+      <c r="J184" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="K164" s="7" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="165" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C165" s="5">
+      <c r="K184" s="7" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="185" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C185" s="5">
         <f t="shared" si="8"/>
         <v>5020</v>
       </c>
-      <c r="D165" s="5">
+      <c r="D185" s="5">
         <v>5</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="E185" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="F185" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="G165" s="5">
+      <c r="G185" s="5">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="H165" s="5">
+      <c r="H185" s="5">
         <v>450000</v>
       </c>
-      <c r="I165" s="5" t="s">
+      <c r="I185" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="J165" s="7" t="s">
+      <c r="J185" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="K165" s="7" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="166" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C166" s="5">
+      <c r="K185" s="7" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="186" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C186" s="5">
         <f t="shared" si="8"/>
         <v>5021</v>
       </c>
-      <c r="D166" s="5">
+      <c r="D186" s="5">
         <v>5</v>
       </c>
-      <c r="E166" s="5" t="s">
+      <c r="E186" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="F186" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="G166" s="5">
+      <c r="G186" s="5">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="H166" s="5">
+      <c r="H186" s="5">
         <v>520000</v>
       </c>
-      <c r="I166" s="5" t="s">
+      <c r="I186" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="J166" s="7" t="s">
+      <c r="J186" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="K166" s="7" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="167" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C167" s="5">
+      <c r="K186" s="7" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="187" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C187" s="5">
         <f t="shared" si="8"/>
         <v>5022</v>
       </c>
-      <c r="D167" s="5">
+      <c r="D187" s="5">
         <v>5</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="E187" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F187" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="G167" s="5">
+      <c r="G187" s="5">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="H167" s="5">
+      <c r="H187" s="5">
         <v>600000</v>
       </c>
-      <c r="I167" s="5" t="s">
+      <c r="I187" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="J167" s="7" t="s">
+      <c r="J187" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="K167" s="7" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="168" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C168" s="5">
+      <c r="K187" s="7" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="188" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C188" s="5">
         <f t="shared" si="8"/>
         <v>5023</v>
       </c>
-      <c r="D168" s="5">
+      <c r="D188" s="5">
         <v>5</v>
       </c>
-      <c r="E168" s="5" t="s">
+      <c r="E188" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F168" s="5" t="s">
+      <c r="F188" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="G168" s="5">
+      <c r="G188" s="5">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="H168" s="5">
+      <c r="H188" s="5">
         <v>680000</v>
       </c>
-      <c r="I168" s="5" t="s">
+      <c r="I188" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="J168" s="7" t="s">
+      <c r="J188" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="K168" s="7" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="169" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C169" s="5">
+      <c r="K188" s="7" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="189" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C189" s="5">
         <f t="shared" si="8"/>
         <v>5024</v>
       </c>
-      <c r="D169" s="5">
+      <c r="D189" s="5">
         <v>5</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="E189" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="F189" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="G169" s="5">
+      <c r="G189" s="5">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="H169" s="5">
+      <c r="H189" s="5">
         <v>760000</v>
       </c>
-      <c r="I169" s="5" t="s">
+      <c r="I189" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="J169" s="7" t="s">
+      <c r="J189" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="K169" s="7" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="170" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C170" s="5">
+      <c r="K189" s="7" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="190" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C190" s="5">
         <f t="shared" si="8"/>
         <v>5025</v>
       </c>
-      <c r="D170" s="5">
+      <c r="D190" s="5">
         <v>5</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="E190" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="F190" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="G170" s="5">
+      <c r="G190" s="5">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="H170" s="5">
+      <c r="H190" s="5">
         <v>850000</v>
       </c>
-      <c r="I170" s="5" t="s">
+      <c r="I190" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="J170" s="7" t="s">
+      <c r="J190" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="K170" s="7" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="171" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C171" s="5">
+      <c r="K190" s="7" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="191" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C191" s="5">
         <f t="shared" si="8"/>
         <v>5026</v>
       </c>
-      <c r="D171" s="5">
+      <c r="D191" s="5">
         <v>5</v>
       </c>
-      <c r="E171" s="5" t="s">
+      <c r="E191" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="F191" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="G171" s="5">
+      <c r="G191" s="5">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="H171" s="5">
+      <c r="H191" s="5">
         <v>1000000</v>
       </c>
-      <c r="I171" s="5" t="s">
+      <c r="I191" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="J171" s="7" t="s">
+      <c r="J191" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="K171" s="7" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="172" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C172" s="5">
+      <c r="K191" s="7" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="192" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C192" s="5">
         <f t="shared" si="8"/>
         <v>5027</v>
       </c>
-      <c r="D172" s="5">
+      <c r="D192" s="5">
         <v>5</v>
       </c>
-      <c r="E172" s="5" t="s">
+      <c r="E192" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="F192" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="G172" s="5">
+      <c r="G192" s="5">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="H172" s="5">
+      <c r="H192" s="5">
         <v>1250000</v>
       </c>
-      <c r="I172" s="5" t="s">
+      <c r="I192" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="J172" s="7" t="s">
+      <c r="J192" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="K172" s="7" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="173" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C173" s="5">
+      <c r="K192" s="7" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="193" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C193" s="5">
         <f t="shared" si="8"/>
         <v>5028</v>
       </c>
-      <c r="D173" s="5">
+      <c r="D193" s="5">
         <v>5</v>
       </c>
-      <c r="E173" s="5" t="s">
+      <c r="E193" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="F193" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="G173" s="5">
+      <c r="G193" s="5">
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="H173" s="5">
+      <c r="H193" s="5">
         <v>1500000</v>
       </c>
-      <c r="I173" s="5" t="s">
+      <c r="I193" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="J173" s="7" t="s">
+      <c r="J193" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="K173" s="7" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="174" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C174" s="5">
+      <c r="K193" s="7" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="194" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C194" s="5">
         <f t="shared" si="8"/>
         <v>5029</v>
       </c>
-      <c r="D174" s="5">
+      <c r="D194" s="5">
         <v>5</v>
       </c>
-      <c r="E174" s="5" t="s">
+      <c r="E194" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="F194" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="G174" s="5">
+      <c r="G194" s="5">
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
-      <c r="H174" s="5">
+      <c r="H194" s="5">
         <v>1750000</v>
       </c>
-      <c r="I174" s="5" t="s">
+      <c r="I194" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="J174" s="7" t="s">
+      <c r="J194" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="K174" s="7" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="175" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C175" s="5">
+      <c r="K194" s="7" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="195" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C195" s="5">
         <f t="shared" si="8"/>
         <v>5030</v>
       </c>
-      <c r="D175" s="5">
+      <c r="D195" s="5">
         <v>5</v>
       </c>
-      <c r="E175" s="5" t="s">
+      <c r="E195" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="F195" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="G175" s="5">
+      <c r="G195" s="5">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="H175" s="5">
+      <c r="H195" s="5">
         <v>2000000</v>
       </c>
-      <c r="I175" s="5" t="s">
+      <c r="I195" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="J175" s="7" t="s">
+      <c r="J195" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="K175" s="7" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="176" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C176" s="5">
+      <c r="K195" s="7" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="196" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C196" s="5">
         <f t="shared" si="8"/>
         <v>5031</v>
       </c>
-      <c r="D176" s="5">
+      <c r="D196" s="5">
         <v>5</v>
       </c>
-      <c r="E176" s="5" t="s">
+      <c r="E196" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="F176" s="5" t="s">
+      <c r="F196" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="G176" s="5">
+      <c r="G196" s="5">
         <f t="shared" si="9"/>
         <v>31</v>
       </c>
-      <c r="H176" s="5">
+      <c r="H196" s="5">
         <v>2500000</v>
       </c>
-      <c r="I176" s="5" t="s">
+      <c r="I196" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="J176" s="7" t="s">
+      <c r="J196" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="K176" s="7" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="177" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C177" s="5">
+      <c r="K196" s="7" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="197" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C197" s="5">
         <f t="shared" si="8"/>
         <v>5032</v>
       </c>
-      <c r="D177" s="5">
+      <c r="D197" s="5">
         <v>5</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="E197" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="F197" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="G177" s="5">
+      <c r="G197" s="5">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
-      <c r="H177" s="5">
+      <c r="H197" s="5">
         <v>3000000</v>
       </c>
-      <c r="I177" s="5" t="s">
+      <c r="I197" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="J177" s="7" t="s">
+      <c r="J197" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="K177" s="7" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="178" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C178" s="5">
+      <c r="K197" s="7" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="198" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C198" s="5">
         <f t="shared" si="8"/>
         <v>5033</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D198" s="5">
         <v>5</v>
       </c>
-      <c r="E178" s="5" t="s">
+      <c r="E198" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="F178" s="5" t="s">
+      <c r="F198" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="G178" s="5">
+      <c r="G198" s="5">
         <f t="shared" si="9"/>
         <v>33</v>
       </c>
-      <c r="H178" s="5">
+      <c r="H198" s="5">
         <v>4000000</v>
       </c>
-      <c r="I178" s="5" t="s">
+      <c r="I198" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="J178" s="7" t="s">
+      <c r="J198" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="K178" s="7" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="179" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C179" s="5">
+      <c r="K198" s="7" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="199" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C199" s="5">
         <f t="shared" si="8"/>
         <v>5034</v>
       </c>
-      <c r="D179" s="5">
+      <c r="D199" s="5">
         <v>5</v>
       </c>
-      <c r="E179" s="5" t="s">
+      <c r="E199" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="F179" s="5" t="s">
+      <c r="F199" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="G179" s="5">
+      <c r="G199" s="5">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
-      <c r="H179" s="5">
+      <c r="H199" s="5">
         <v>5000000</v>
       </c>
-      <c r="I179" s="5" t="s">
+      <c r="I199" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="J179" s="7" t="s">
+      <c r="J199" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="K179" s="7" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="180" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C180" s="5">
+      <c r="K199" s="7" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="200" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C200" s="5">
         <f t="shared" si="8"/>
         <v>5035</v>
       </c>
-      <c r="D180" s="5">
+      <c r="D200" s="5">
         <v>5</v>
       </c>
-      <c r="E180" s="5" t="s">
+      <c r="E200" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F200" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="G180" s="5">
+      <c r="G200" s="5">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="H180" s="5">
+      <c r="H200" s="5">
         <v>6000000</v>
       </c>
-      <c r="I180" s="5" t="s">
+      <c r="I200" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="J180" s="7" t="s">
+      <c r="J200" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="K180" s="7" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="181" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C181" s="5">
+      <c r="K200" s="7" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="201" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C201" s="5">
+        <f t="shared" si="8"/>
+        <v>5036</v>
+      </c>
+      <c r="D201" s="5">
+        <v>5</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G201" s="5">
+        <f t="shared" si="9"/>
+        <v>36</v>
+      </c>
+      <c r="H201" s="5">
+        <v>7500000</v>
+      </c>
+      <c r="I201" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J201" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K201" s="7" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="202" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C202" s="5">
+        <f t="shared" si="8"/>
+        <v>5037</v>
+      </c>
+      <c r="D202" s="5">
+        <v>5</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G202" s="5">
+        <f t="shared" si="9"/>
+        <v>37</v>
+      </c>
+      <c r="H202" s="5">
+        <v>9000000</v>
+      </c>
+      <c r="I202" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K202" s="7" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="203" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C203" s="5">
+        <f t="shared" si="8"/>
+        <v>5038</v>
+      </c>
+      <c r="D203" s="5">
+        <v>5</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G203" s="5">
+        <f t="shared" si="9"/>
+        <v>38</v>
+      </c>
+      <c r="H203" s="5">
+        <v>10500000</v>
+      </c>
+      <c r="I203" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J203" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K203" s="7" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="204" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C204" s="5">
+        <f t="shared" si="8"/>
+        <v>5039</v>
+      </c>
+      <c r="D204" s="5">
+        <v>5</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G204" s="5">
+        <f t="shared" si="9"/>
+        <v>39</v>
+      </c>
+      <c r="H204" s="5">
+        <v>12000000</v>
+      </c>
+      <c r="I204" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J204" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K204" s="7" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="205" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C205" s="5">
+        <f t="shared" si="8"/>
+        <v>5040</v>
+      </c>
+      <c r="D205" s="5">
+        <v>5</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G205" s="5">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="H205" s="5">
+        <v>14000000</v>
+      </c>
+      <c r="I205" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="J205" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="K205" s="7" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="206" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C206" s="5">
         <v>6001</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D206" s="5">
         <v>6</v>
       </c>
-      <c r="E181" s="5" t="s">
+      <c r="E206" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="F181" s="5" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G181" s="5">
+      <c r="F206" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="G206" s="5">
         <v>1</v>
       </c>
-      <c r="H181" s="5">
+      <c r="H206" s="5">
         <v>3000</v>
       </c>
-      <c r="I181" s="5" t="s">
+      <c r="I206" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="J181" s="7" t="str">
-        <f>"生命上限提升+"&amp;G181&amp;"%,眩晕抵抗概率+"&amp;G181&amp;"%"</f>
+      <c r="J206" s="7" t="str">
+        <f>"生命上限提升+"&amp;G206&amp;"%,眩晕抵抗概率+"&amp;G206&amp;"%"</f>
         <v>生命上限提升+1%,眩晕抵抗概率+1%</v>
       </c>
-      <c r="K181" s="7" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="182" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C182" s="5">
+      <c r="K206" s="7" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="207" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C207" s="5">
         <v>6002</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D207" s="5">
         <v>6</v>
       </c>
-      <c r="E182" s="5" t="s">
+      <c r="E207" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="F182" s="5" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G182" s="5">
+      <c r="F207" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="G207" s="5">
         <v>2</v>
       </c>
-      <c r="H182" s="5">
+      <c r="H207" s="5">
         <v>6000</v>
       </c>
-      <c r="I182" s="5" t="s">
+      <c r="I207" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="J182" s="7" t="str">
-        <f t="shared" ref="J182:J200" si="10">"生命上限提升+"&amp;G182&amp;"%,眩晕抵抗概率+"&amp;G182&amp;"%"</f>
+      <c r="J207" s="7" t="str">
+        <f t="shared" ref="J207:J225" si="10">"生命上限提升+"&amp;G207&amp;"%,眩晕抵抗概率+"&amp;G207&amp;"%"</f>
         <v>生命上限提升+2%,眩晕抵抗概率+2%</v>
       </c>
-      <c r="K182" s="7" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="183" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C183" s="5">
+      <c r="K207" s="7" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="208" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C208" s="5">
         <v>6003</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D208" s="5">
         <v>6</v>
       </c>
-      <c r="E183" s="5" t="s">
+      <c r="E208" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="F183" s="5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G183" s="5">
+      <c r="F208" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G208" s="5">
         <v>3</v>
       </c>
-      <c r="H183" s="5">
+      <c r="H208" s="5">
         <v>10000</v>
       </c>
-      <c r="I183" s="5" t="s">
+      <c r="I208" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="J183" s="7" t="str">
+      <c r="J208" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+3%,眩晕抵抗概率+3%</v>
       </c>
-      <c r="K183" s="7" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="184" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C184" s="5">
+      <c r="K208" s="7" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="209" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C209" s="5">
         <v>6004</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D209" s="5">
         <v>6</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E209" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="F184" s="5" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G184" s="5">
+      <c r="F209" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G209" s="5">
         <v>4</v>
       </c>
-      <c r="H184" s="5">
+      <c r="H209" s="5">
         <v>15000</v>
       </c>
-      <c r="I184" s="5" t="s">
+      <c r="I209" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="J184" s="7" t="str">
+      <c r="J209" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+4%,眩晕抵抗概率+4%</v>
       </c>
-      <c r="K184" s="7" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="185" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C185" s="5">
+      <c r="K209" s="7" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="210" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C210" s="5">
         <v>6005</v>
       </c>
-      <c r="D185" s="5">
+      <c r="D210" s="5">
         <v>6</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="E210" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G185" s="5">
+      <c r="F210" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G210" s="5">
         <v>5</v>
       </c>
-      <c r="H185" s="5">
+      <c r="H210" s="5">
         <v>22500</v>
       </c>
-      <c r="I185" s="5" t="s">
+      <c r="I210" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="J185" s="7" t="str">
+      <c r="J210" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+5%,眩晕抵抗概率+5%</v>
       </c>
-      <c r="K185" s="7" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="186" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C186" s="5">
+      <c r="K210" s="7" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="211" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C211" s="5">
         <v>6006</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D211" s="5">
         <v>6</v>
       </c>
-      <c r="E186" s="5" t="s">
+      <c r="E211" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="F186" s="5" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G186" s="5">
+      <c r="F211" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G211" s="5">
         <v>6</v>
       </c>
-      <c r="H186" s="5">
+      <c r="H211" s="5">
         <v>32500</v>
       </c>
-      <c r="I186" s="5" t="s">
+      <c r="I211" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="J186" s="7" t="str">
+      <c r="J211" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+6%,眩晕抵抗概率+6%</v>
       </c>
-      <c r="K186" s="7" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="187" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C187" s="5">
+      <c r="K211" s="7" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="212" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C212" s="5">
         <v>6007</v>
       </c>
-      <c r="D187" s="5">
+      <c r="D212" s="5">
         <v>6</v>
       </c>
-      <c r="E187" s="5" t="s">
+      <c r="E212" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="F187" s="5" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G187" s="5">
+      <c r="F212" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G212" s="5">
         <v>7</v>
       </c>
-      <c r="H187" s="5">
+      <c r="H212" s="5">
         <v>45000</v>
       </c>
-      <c r="I187" s="5" t="s">
+      <c r="I212" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="J187" s="7" t="str">
+      <c r="J212" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+7%,眩晕抵抗概率+7%</v>
       </c>
-      <c r="K187" s="7" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="188" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C188" s="5">
+      <c r="K212" s="7" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="213" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C213" s="5">
         <v>6008</v>
       </c>
-      <c r="D188" s="5">
+      <c r="D213" s="5">
         <v>6</v>
       </c>
-      <c r="E188" s="5" t="s">
+      <c r="E213" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="F188" s="5" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G188" s="5">
+      <c r="F213" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G213" s="5">
         <v>8</v>
       </c>
-      <c r="H188" s="5">
+      <c r="H213" s="5">
         <v>60000</v>
       </c>
-      <c r="I188" s="5" t="s">
+      <c r="I213" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="J188" s="7" t="str">
+      <c r="J213" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+8%,眩晕抵抗概率+8%</v>
       </c>
-      <c r="K188" s="7" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="189" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C189" s="5">
+      <c r="K213" s="7" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="214" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C214" s="5">
         <v>6009</v>
       </c>
-      <c r="D189" s="5">
+      <c r="D214" s="5">
         <v>6</v>
       </c>
-      <c r="E189" s="5" t="s">
+      <c r="E214" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F189" s="5" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G189" s="5">
+      <c r="F214" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G214" s="5">
         <v>9</v>
       </c>
-      <c r="H189" s="5">
+      <c r="H214" s="5">
         <v>80000</v>
       </c>
-      <c r="I189" s="5" t="s">
+      <c r="I214" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="J189" s="7" t="str">
+      <c r="J214" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+9%,眩晕抵抗概率+9%</v>
       </c>
-      <c r="K189" s="7" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="190" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C190" s="5">
+      <c r="K214" s="7" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="215" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C215" s="5">
         <v>6010</v>
       </c>
-      <c r="D190" s="5">
+      <c r="D215" s="5">
         <v>6</v>
       </c>
-      <c r="E190" s="5" t="s">
+      <c r="E215" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G190" s="5">
+      <c r="F215" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G215" s="5">
         <v>10</v>
       </c>
-      <c r="H190" s="5">
+      <c r="H215" s="5">
         <v>100000</v>
       </c>
-      <c r="I190" s="5" t="s">
+      <c r="I215" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="J190" s="7" t="str">
+      <c r="J215" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+10%,眩晕抵抗概率+10%</v>
       </c>
-      <c r="K190" s="7" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="191" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C191" s="5">
+      <c r="K215" s="7" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="216" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C216" s="5">
         <v>6011</v>
       </c>
-      <c r="D191" s="5">
+      <c r="D216" s="5">
         <v>6</v>
       </c>
-      <c r="E191" s="5" t="s">
+      <c r="E216" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="F191" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G191" s="5">
+      <c r="F216" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G216" s="5">
         <v>11</v>
       </c>
-      <c r="H191" s="5">
+      <c r="H216" s="5">
         <v>120000</v>
       </c>
-      <c r="I191" s="5" t="s">
+      <c r="I216" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="J191" s="7" t="str">
+      <c r="J216" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+11%,眩晕抵抗概率+11%</v>
       </c>
-      <c r="K191" s="7" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="192" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C192" s="5">
+      <c r="K216" s="7" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="217" spans="3:11" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C217" s="5">
         <v>6012</v>
       </c>
-      <c r="D192" s="5">
+      <c r="D217" s="5">
         <v>6</v>
       </c>
-      <c r="E192" s="5" t="s">
+      <c r="E217" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="F192" s="5" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G192" s="5">
+      <c r="F217" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G217" s="5">
         <v>12</v>
       </c>
-      <c r="H192" s="5">
+      <c r="H217" s="5">
         <v>140000</v>
       </c>
-      <c r="I192" s="5" t="s">
+      <c r="I217" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="J192" s="7" t="str">
+      <c r="J217" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+12%,眩晕抵抗概率+12%</v>
       </c>
-      <c r="K192" s="7" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="193" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C193" s="5">
+      <c r="K217" s="7" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="218" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C218" s="5">
         <v>6013</v>
       </c>
-      <c r="D193" s="5">
+      <c r="D218" s="5">
         <v>6</v>
       </c>
-      <c r="E193" s="5" t="s">
+      <c r="E218" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="F193" s="5" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G193" s="5">
+      <c r="F218" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G218" s="5">
         <v>13</v>
       </c>
-      <c r="H193" s="5">
+      <c r="H218" s="5">
         <v>160000</v>
       </c>
-      <c r="I193" s="5" t="s">
+      <c r="I218" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="J193" s="7" t="str">
+      <c r="J218" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+13%,眩晕抵抗概率+13%</v>
       </c>
-      <c r="K193" s="7" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="194" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C194" s="5">
+      <c r="K218" s="7" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="219" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C219" s="5">
         <v>6014</v>
       </c>
-      <c r="D194" s="5">
+      <c r="D219" s="5">
         <v>6</v>
       </c>
-      <c r="E194" s="5" t="s">
+      <c r="E219" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="F194" s="5" t="s">
-        <v>1014</v>
-      </c>
-      <c r="G194" s="5">
+      <c r="F219" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G219" s="5">
         <v>14</v>
       </c>
-      <c r="H194" s="5">
+      <c r="H219" s="5">
         <v>180000</v>
       </c>
-      <c r="I194" s="5" t="s">
+      <c r="I219" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="J194" s="7" t="str">
+      <c r="J219" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+14%,眩晕抵抗概率+14%</v>
       </c>
-      <c r="K194" s="7" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="195" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C195" s="5">
+      <c r="K219" s="7" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="220" spans="3:11" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C220" s="5">
         <v>6015</v>
       </c>
-      <c r="D195" s="5">
+      <c r="D220" s="5">
         <v>6</v>
       </c>
-      <c r="E195" s="5" t="s">
+      <c r="E220" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="F195" s="5" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G195" s="5">
+      <c r="F220" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G220" s="5">
         <v>15</v>
       </c>
-      <c r="H195" s="5">
+      <c r="H220" s="5">
         <v>200000</v>
       </c>
-      <c r="I195" s="5" t="s">
+      <c r="I220" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="J195" s="7" t="str">
+      <c r="J220" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+15%,眩晕抵抗概率+15%</v>
       </c>
-      <c r="K195" s="7" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="196" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C196" s="5">
-        <f>C195+1</f>
+      <c r="K220" s="7" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="221" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C221" s="5">
+        <f>C220+1</f>
         <v>6016</v>
       </c>
-      <c r="D196" s="5">
+      <c r="D221" s="5">
         <v>6</v>
       </c>
-      <c r="E196" s="5" t="s">
+      <c r="E221" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="F196" s="5" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G196" s="5">
-        <f>G195+1</f>
+      <c r="F221" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G221" s="5">
+        <f>G220+1</f>
         <v>16</v>
       </c>
-      <c r="H196" s="5">
+      <c r="H221" s="5">
         <v>230000</v>
       </c>
-      <c r="I196" s="5" t="s">
+      <c r="I221" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="J196" s="7" t="str">
+      <c r="J221" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+16%,眩晕抵抗概率+16%</v>
       </c>
-      <c r="K196" s="7" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="197" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C197" s="5">
-        <f t="shared" ref="C197:C210" si="11">C196+1</f>
+      <c r="K221" s="7" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="222" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C222" s="5">
+        <f t="shared" ref="C222:C235" si="11">C221+1</f>
         <v>6017</v>
       </c>
-      <c r="D197" s="5">
+      <c r="D222" s="5">
         <v>6</v>
       </c>
-      <c r="E197" s="5" t="s">
+      <c r="E222" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="F197" s="5" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G197" s="5">
-        <f t="shared" ref="G197:G210" si="12">G196+1</f>
+      <c r="F222" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G222" s="5">
+        <f t="shared" ref="G222:G235" si="12">G221+1</f>
         <v>17</v>
       </c>
-      <c r="H197" s="5">
+      <c r="H222" s="5">
         <v>270000</v>
       </c>
-      <c r="I197" s="5" t="s">
+      <c r="I222" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="J197" s="7" t="str">
+      <c r="J222" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+17%,眩晕抵抗概率+17%</v>
       </c>
-      <c r="K197" s="7" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="198" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C198" s="5">
+      <c r="K222" s="7" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="223" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C223" s="5">
         <f t="shared" si="11"/>
         <v>6018</v>
       </c>
-      <c r="D198" s="5">
+      <c r="D223" s="5">
         <v>6</v>
       </c>
-      <c r="E198" s="5" t="s">
+      <c r="E223" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="F198" s="5" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G198" s="5">
+      <c r="F223" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G223" s="5">
         <f t="shared" si="12"/>
         <v>18</v>
       </c>
-      <c r="H198" s="5">
+      <c r="H223" s="5">
         <v>320000</v>
       </c>
-      <c r="I198" s="5" t="s">
+      <c r="I223" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="J198" s="7" t="str">
+      <c r="J223" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+18%,眩晕抵抗概率+18%</v>
       </c>
-      <c r="K198" s="7" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="199" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C199" s="5">
+      <c r="K223" s="7" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="224" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C224" s="5">
         <f t="shared" si="11"/>
         <v>6019</v>
       </c>
-      <c r="D199" s="5">
+      <c r="D224" s="5">
         <v>6</v>
       </c>
-      <c r="E199" s="5" t="s">
+      <c r="E224" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="F199" s="5" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G199" s="5">
+      <c r="F224" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G224" s="5">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="H199" s="5">
+      <c r="H224" s="5">
         <v>380000</v>
       </c>
-      <c r="I199" s="5" t="s">
+      <c r="I224" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="J199" s="7" t="str">
+      <c r="J224" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+19%,眩晕抵抗概率+19%</v>
       </c>
-      <c r="K199" s="7" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="200" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C200" s="5">
+      <c r="K224" s="7" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="225" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C225" s="5">
         <f t="shared" si="11"/>
         <v>6020</v>
       </c>
-      <c r="D200" s="5">
+      <c r="D225" s="5">
         <v>6</v>
       </c>
-      <c r="E200" s="5" t="s">
+      <c r="E225" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="F200" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G200" s="5">
+      <c r="F225" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G225" s="5">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="H200" s="5">
+      <c r="H225" s="5">
         <v>450000</v>
       </c>
-      <c r="I200" s="5" t="s">
+      <c r="I225" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="J200" s="7" t="str">
+      <c r="J225" s="7" t="str">
         <f t="shared" si="10"/>
         <v>生命上限提升+20%,眩晕抵抗概率+20%</v>
       </c>
-      <c r="K200" s="7" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="201" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C201" s="5">
+      <c r="K225" s="7" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="226" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C226" s="5">
         <f t="shared" si="11"/>
         <v>6021</v>
       </c>
-      <c r="D201" s="5">
+      <c r="D226" s="5">
         <v>6</v>
       </c>
-      <c r="E201" s="5" t="s">
+      <c r="E226" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="F201" s="5" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G201" s="5">
+      <c r="F226" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G226" s="5">
         <f t="shared" si="12"/>
         <v>21</v>
       </c>
-      <c r="H201" s="5">
+      <c r="H226" s="5">
         <v>520000</v>
       </c>
-      <c r="I201" s="5" t="s">
+      <c r="I226" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="J201" s="5" t="str">
-        <f t="shared" ref="J201:J205" si="13">"生命上限提升+"&amp;G201&amp;"%,眩晕抵抗概率+"&amp;G201&amp;"%"</f>
+      <c r="J226" s="5" t="str">
+        <f t="shared" ref="J226:J230" si="13">"生命上限提升+"&amp;G226&amp;"%,眩晕抵抗概率+"&amp;G226&amp;"%"</f>
         <v>生命上限提升+21%,眩晕抵抗概率+21%</v>
       </c>
-      <c r="K201" s="7" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="202" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C202" s="5">
+      <c r="K226" s="7" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="227" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C227" s="5">
         <f t="shared" si="11"/>
         <v>6022</v>
       </c>
-      <c r="D202" s="5">
+      <c r="D227" s="5">
         <v>6</v>
       </c>
-      <c r="E202" s="5" t="s">
+      <c r="E227" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="F202" s="5" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G202" s="5">
+      <c r="F227" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G227" s="5">
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="H202" s="5">
+      <c r="H227" s="5">
         <v>600000</v>
       </c>
-      <c r="I202" s="5" t="s">
+      <c r="I227" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="J202" s="5" t="str">
+      <c r="J227" s="5" t="str">
         <f t="shared" si="13"/>
         <v>生命上限提升+22%,眩晕抵抗概率+22%</v>
       </c>
-      <c r="K202" s="7" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="203" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C203" s="5">
+      <c r="K227" s="7" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="228" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C228" s="5">
         <f t="shared" si="11"/>
         <v>6023</v>
       </c>
-      <c r="D203" s="5">
+      <c r="D228" s="5">
         <v>6</v>
       </c>
-      <c r="E203" s="5" t="s">
+      <c r="E228" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="F203" s="5" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G203" s="5">
+      <c r="F228" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G228" s="5">
         <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="H203" s="5">
+      <c r="H228" s="5">
         <v>680000</v>
       </c>
-      <c r="I203" s="5" t="s">
+      <c r="I228" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="J203" s="5" t="str">
+      <c r="J228" s="5" t="str">
         <f t="shared" si="13"/>
         <v>生命上限提升+23%,眩晕抵抗概率+23%</v>
       </c>
-      <c r="K203" s="7" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="204" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C204" s="5">
+      <c r="K228" s="7" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="229" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C229" s="5">
         <f t="shared" si="11"/>
         <v>6024</v>
       </c>
-      <c r="D204" s="5">
+      <c r="D229" s="5">
         <v>6</v>
       </c>
-      <c r="E204" s="5" t="s">
+      <c r="E229" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="F204" s="5" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G204" s="5">
+      <c r="F229" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G229" s="5">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="H204" s="5">
+      <c r="H229" s="5">
         <v>760000</v>
       </c>
-      <c r="I204" s="5" t="s">
+      <c r="I229" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="J204" s="5" t="str">
+      <c r="J229" s="5" t="str">
         <f t="shared" si="13"/>
         <v>生命上限提升+24%,眩晕抵抗概率+24%</v>
       </c>
-      <c r="K204" s="7" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="205" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C205" s="5">
+      <c r="K229" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="230" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C230" s="5">
         <f t="shared" si="11"/>
         <v>6025</v>
       </c>
-      <c r="D205" s="5">
+      <c r="D230" s="5">
         <v>6</v>
       </c>
-      <c r="E205" s="5" t="s">
+      <c r="E230" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="F205" s="5" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G205" s="5">
+      <c r="F230" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G230" s="5">
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="H205" s="5">
+      <c r="H230" s="5">
         <v>850000</v>
       </c>
-      <c r="I205" s="5" t="s">
+      <c r="I230" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="J205" s="5" t="str">
+      <c r="J230" s="5" t="str">
         <f t="shared" si="13"/>
         <v>生命上限提升+25%,眩晕抵抗概率+25%</v>
       </c>
-      <c r="K205" s="7" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="206" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C206" s="5">
+      <c r="K230" s="7" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="231" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C231" s="5">
         <f t="shared" si="11"/>
         <v>6026</v>
       </c>
-      <c r="D206" s="5">
+      <c r="D231" s="5">
         <v>6</v>
       </c>
-      <c r="E206" s="5" t="s">
+      <c r="E231" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="F206" s="5" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G206" s="5">
+      <c r="F231" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G231" s="5">
         <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="H206" s="5">
+      <c r="H231" s="5">
         <v>1000000</v>
       </c>
-      <c r="I206" s="5" t="s">
+      <c r="I231" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="J206" s="5" t="str">
-        <f t="shared" ref="J206:J215" si="14">"生命上限提升+"&amp;G206&amp;"%,眩晕抵抗概率+"&amp;G206&amp;"%"</f>
+      <c r="J231" s="5" t="str">
+        <f t="shared" ref="J231:J240" si="14">"生命上限提升+"&amp;G231&amp;"%,眩晕抵抗概率+"&amp;G231&amp;"%"</f>
         <v>生命上限提升+26%,眩晕抵抗概率+26%</v>
       </c>
-      <c r="K206" s="7" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="207" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C207" s="5">
+      <c r="K231" s="7" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="232" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C232" s="5">
         <f t="shared" si="11"/>
         <v>6027</v>
       </c>
-      <c r="D207" s="5">
+      <c r="D232" s="5">
         <v>6</v>
       </c>
-      <c r="E207" s="5" t="s">
+      <c r="E232" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="F207" s="5" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G207" s="5">
+      <c r="F232" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G232" s="5">
         <f t="shared" si="12"/>
         <v>27</v>
       </c>
-      <c r="H207" s="5">
+      <c r="H232" s="5">
         <v>1250000</v>
       </c>
-      <c r="I207" s="5" t="s">
+      <c r="I232" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="J207" s="5" t="str">
+      <c r="J232" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+27%,眩晕抵抗概率+27%</v>
       </c>
-      <c r="K207" s="7" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="208" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C208" s="5">
+      <c r="K232" s="7" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="233" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C233" s="5">
         <f t="shared" si="11"/>
         <v>6028</v>
       </c>
-      <c r="D208" s="5">
+      <c r="D233" s="5">
         <v>6</v>
       </c>
-      <c r="E208" s="5" t="s">
+      <c r="E233" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F208" s="5" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G208" s="5">
+      <c r="F233" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G233" s="5">
         <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="H208" s="5">
+      <c r="H233" s="5">
         <v>1500000</v>
       </c>
-      <c r="I208" s="5" t="s">
+      <c r="I233" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="J208" s="5" t="str">
+      <c r="J233" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+28%,眩晕抵抗概率+28%</v>
       </c>
-      <c r="K208" s="7" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="209" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C209" s="5">
+      <c r="K233" s="7" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="234" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C234" s="5">
         <f t="shared" si="11"/>
         <v>6029</v>
       </c>
-      <c r="D209" s="5">
+      <c r="D234" s="5">
         <v>6</v>
       </c>
-      <c r="E209" s="5" t="s">
+      <c r="E234" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="F209" s="5" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G209" s="5">
+      <c r="F234" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G234" s="5">
         <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="H209" s="5">
+      <c r="H234" s="5">
         <v>1750000</v>
       </c>
-      <c r="I209" s="5" t="s">
+      <c r="I234" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="J209" s="5" t="str">
+      <c r="J234" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+29%,眩晕抵抗概率+29%</v>
       </c>
-      <c r="K209" s="7" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="210" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C210" s="5">
+      <c r="K234" s="7" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="235" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C235" s="5">
         <f t="shared" si="11"/>
         <v>6030</v>
       </c>
-      <c r="D210" s="5">
+      <c r="D235" s="5">
         <v>6</v>
       </c>
-      <c r="E210" s="5" t="s">
+      <c r="E235" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="F210" s="5" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G210" s="5">
+      <c r="F235" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G235" s="5">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="H210" s="5">
+      <c r="H235" s="5">
         <v>2000000</v>
       </c>
-      <c r="I210" s="5" t="s">
+      <c r="I235" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="J210" s="5" t="str">
+      <c r="J235" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+30%,眩晕抵抗概率+30%</v>
       </c>
-      <c r="K210" s="7" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="211" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C211" s="9">
-        <f t="shared" ref="C211:C215" si="15">C210+1</f>
+      <c r="K235" s="7" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="236" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C236" s="9">
+        <f t="shared" ref="C236:C245" si="15">C235+1</f>
         <v>6031</v>
       </c>
-      <c r="D211" s="5">
+      <c r="D236" s="5">
         <v>6</v>
       </c>
-      <c r="E211" s="5" t="s">
+      <c r="E236" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="F211" s="5" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G211" s="9">
-        <f t="shared" ref="G211:G215" si="16">G210+1</f>
+      <c r="F236" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G236" s="9">
+        <f t="shared" ref="G236:G245" si="16">G235+1</f>
         <v>31</v>
       </c>
-      <c r="H211" s="5">
+      <c r="H236" s="5">
         <v>2500000</v>
       </c>
-      <c r="I211" s="5" t="s">
+      <c r="I236" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="J211" s="5" t="str">
+      <c r="J236" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+31%,眩晕抵抗概率+31%</v>
       </c>
-      <c r="K211" s="7" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="212" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C212" s="9">
+      <c r="K236" s="7" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="237" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C237" s="9">
         <f t="shared" si="15"/>
         <v>6032</v>
       </c>
-      <c r="D212" s="5">
+      <c r="D237" s="5">
         <v>6</v>
       </c>
-      <c r="E212" s="5" t="s">
+      <c r="E237" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="F212" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G212" s="9">
+      <c r="F237" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G237" s="9">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
-      <c r="H212" s="5">
+      <c r="H237" s="5">
         <v>3000000</v>
       </c>
-      <c r="I212" s="5" t="s">
+      <c r="I237" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="J212" s="5" t="str">
+      <c r="J237" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+32%,眩晕抵抗概率+32%</v>
       </c>
-      <c r="K212" s="7" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="213" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B213" s="10"/>
-      <c r="C213" s="9">
+      <c r="K237" s="7" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="238" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B238" s="10"/>
+      <c r="C238" s="9">
         <f t="shared" si="15"/>
         <v>6033</v>
       </c>
-      <c r="D213" s="5">
+      <c r="D238" s="5">
         <v>6</v>
       </c>
-      <c r="E213" s="5" t="s">
+      <c r="E238" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="F213" s="5" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G213" s="9">
+      <c r="F238" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G238" s="9">
         <f t="shared" si="16"/>
         <v>33</v>
       </c>
-      <c r="H213" s="5">
+      <c r="H238" s="5">
         <v>4000000</v>
       </c>
-      <c r="I213" s="5" t="s">
+      <c r="I238" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="J213" s="5" t="str">
+      <c r="J238" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+33%,眩晕抵抗概率+33%</v>
       </c>
-      <c r="K213" s="7" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="214" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C214" s="9">
+      <c r="K238" s="7" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="239" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C239" s="9">
         <f t="shared" si="15"/>
         <v>6034</v>
       </c>
-      <c r="D214" s="5">
+      <c r="D239" s="5">
         <v>6</v>
       </c>
-      <c r="E214" s="5" t="s">
+      <c r="E239" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="F214" s="5" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G214" s="9">
+      <c r="F239" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G239" s="9">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
-      <c r="H214" s="5">
+      <c r="H239" s="5">
         <v>5000000</v>
       </c>
-      <c r="I214" s="5" t="s">
+      <c r="I239" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="J214" s="5" t="str">
+      <c r="J239" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+34%,眩晕抵抗概率+34%</v>
       </c>
-      <c r="K214" s="7" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="215" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C215" s="9">
+      <c r="K239" s="7" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="240" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C240" s="9">
         <f t="shared" si="15"/>
         <v>6035</v>
       </c>
-      <c r="D215" s="5">
+      <c r="D240" s="5">
         <v>6</v>
       </c>
-      <c r="E215" s="5" t="s">
+      <c r="E240" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="F215" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G215" s="9">
+      <c r="F240" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G240" s="9">
         <f t="shared" si="16"/>
         <v>35</v>
       </c>
-      <c r="H215" s="5">
+      <c r="H240" s="5">
         <v>6000000</v>
       </c>
-      <c r="I215" s="5" t="s">
+      <c r="I240" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="J215" s="5" t="str">
+      <c r="J240" s="5" t="str">
         <f t="shared" si="14"/>
         <v>生命上限提升+35%,眩晕抵抗概率+35%</v>
       </c>
-      <c r="K215" s="7" t="s">
-        <v>1000</v>
+      <c r="K240" s="7" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="241" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C241" s="9">
+        <f>C240+1</f>
+        <v>6036</v>
+      </c>
+      <c r="D241" s="5">
+        <v>6</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G241" s="9">
+        <f>G240+1</f>
+        <v>36</v>
+      </c>
+      <c r="H241" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I241" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J241" s="5" t="str">
+        <f t="shared" ref="J241:J245" si="17">"生命上限提升+"&amp;G241&amp;"%,眩晕抵抗概率+"&amp;G241&amp;"%"</f>
+        <v>生命上限提升+36%,眩晕抵抗概率+36%</v>
+      </c>
+      <c r="K241" s="7" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="242" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C242" s="9">
+        <f t="shared" si="15"/>
+        <v>6037</v>
+      </c>
+      <c r="D242" s="5">
+        <v>6</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G242" s="9">
+        <f t="shared" si="16"/>
+        <v>37</v>
+      </c>
+      <c r="H242" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I242" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="J242" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>生命上限提升+37%,眩晕抵抗概率+37%</v>
+      </c>
+      <c r="K242" s="7" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="243" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C243" s="9">
+        <f t="shared" si="15"/>
+        <v>6038</v>
+      </c>
+      <c r="D243" s="5">
+        <v>6</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G243" s="9">
+        <f t="shared" si="16"/>
+        <v>38</v>
+      </c>
+      <c r="H243" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I243" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J243" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>生命上限提升+38%,眩晕抵抗概率+38%</v>
+      </c>
+      <c r="K243" s="7" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="244" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C244" s="9">
+        <f t="shared" si="15"/>
+        <v>6039</v>
+      </c>
+      <c r="D244" s="5">
+        <v>6</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G244" s="9">
+        <f t="shared" si="16"/>
+        <v>39</v>
+      </c>
+      <c r="H244" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I244" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J244" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>生命上限提升+39%,眩晕抵抗概率+39%</v>
+      </c>
+      <c r="K244" s="7" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="245" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C245" s="9">
+        <f t="shared" si="15"/>
+        <v>6040</v>
+      </c>
+      <c r="D245" s="5">
+        <v>6</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G245" s="9">
+        <f t="shared" si="16"/>
+        <v>40</v>
+      </c>
+      <c r="H245" s="5">
+        <v>6000000</v>
+      </c>
+      <c r="I245" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="J245" s="5" t="str">
+        <f t="shared" si="17"/>
+        <v>生命上限提升+40%,眩晕抵抗概率+40%</v>
+      </c>
+      <c r="K245" s="7" t="s">
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
